--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -19,7 +19,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="320">
   <si>
     <t>Тестовые сценарии автоматизированного тестирования мобильного приложения "В Хосписе"
-Устройство Samsung Galaxy S20FE, модель SM-G780G/DSM, ОС Android 13, API 30</t>
+Устройство Samsung Galaxy S20FE, модель SM-G780G/DSM, ОС Android 13, API 36</t>
   </si>
   <si>
     <t>ID</t>

--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="hICtKVFO41xUw3XT5yuiru15Ql9eWSGAlQ7m972FXl0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Aj7VA9lapY0FXdfm/QwQOE6U3XXXbge0CKvhHPO6Zek="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="299">
   <si>
     <t>Тестовые сценарии автоматизированного тестирования мобильного приложения "В Хосписе"
 Устройство Samsung Galaxy S20FE, модель SM-G780G/DSM, ОС Android 13, API 36</t>
@@ -325,652 +325,589 @@
     <t>ТС-016</t>
   </si>
   <si>
-    <t>Переход в раздел "О приложении" через главное меню</t>
+    <t>Переход на главную страницу приложения через главное меню</t>
   </si>
   <si>
     <t>1. На верхней панели приложения выбрать и нажать на иконку "Меню"</t>
   </si>
   <si>
-    <t>2. В появившемся списке нажать на строку "О приложении"</t>
-  </si>
-  <si>
-    <t>2. Произошел переход на страницу "О приложении"</t>
+    <t>2. В появившемся списке нажать на строку "Главная"</t>
+  </si>
+  <si>
+    <t>2. Ссылка на страницу "Главная" не активна</t>
   </si>
   <si>
     <t>ТС-017</t>
   </si>
   <si>
-    <t>Переход на главную страницу приложения через главное меню</t>
-  </si>
-  <si>
-    <t>2. В появившемся списке нажать на строку "Главная"</t>
-  </si>
-  <si>
-    <t>2. Ссылка на страницу "Главная" не активна</t>
+    <t>Переход в раздел "Цитаты" через кнопку на панели управления приложения</t>
+  </si>
+  <si>
+    <t>1. На верхней панели приложения выбрать и нажать на иконку "Цитаты" (в виде логотипа приложения)</t>
+  </si>
+  <si>
+    <t>1. Иконка "Цитаты" активна, после нажатия произошел переход на страницу тематических цитат "Главное - жить любя"</t>
+  </si>
+  <si>
+    <t>3. Страница "Цитаты"</t>
   </si>
   <si>
     <t>ТС-018</t>
   </si>
   <si>
-    <t>Переход в раздел "Цитаты" через кнопку на панели управления приложения</t>
-  </si>
-  <si>
-    <t>1. На верхней панели приложения выбрать и нажать на иконку "Цитаты" (в виде логотипа приложения)</t>
-  </si>
-  <si>
-    <t>1. Иконка "Цитаты" активна, после нажатия произошел переход на страницу тематических цитат "Главное - жить любя"</t>
-  </si>
-  <si>
-    <t>3. Страница информации о приложении</t>
+    <t>Возможность развернуть для чтения цитату на выбор</t>
+  </si>
+  <si>
+    <t>Пользователь успешно авторизован в приложении, путем нажатии на иконку "Цитаты" перешел на страницу "Главное - жить любя"</t>
+  </si>
+  <si>
+    <t>1. Пролистать список цитат вниз, выбрать шестую сверху цитату и нажать на стрелочку над заголовком цитаты</t>
+  </si>
+  <si>
+    <t>1. В раскрывшемся окошке появляется текст выбранной цитаты</t>
   </si>
   <si>
     <t>ТС-019</t>
   </si>
   <si>
-    <t>Работа ссылки "Политика конфиденциальности"</t>
-  </si>
-  <si>
-    <t>Пользователь успешно авторизован в приложении.</t>
-  </si>
-  <si>
-    <t>3. На странице информации о приложении нажать на ссылку под заголовком "Политика конфиденциальности"</t>
-  </si>
-  <si>
-    <t>3. Произошел переход на страницу, описывающую политику конфиденциальности</t>
+    <t>2. Произошел переход на главную страницу приложения</t>
   </si>
   <si>
     <t>ТС-020</t>
   </si>
   <si>
-    <t>Работа ссылки "Пользовательское соглашение"</t>
-  </si>
-  <si>
-    <t>3. На странице информации о приложении нажать на ссылку под заголовком "Пользовательское соглашение"</t>
-  </si>
-  <si>
-    <t>3. Произошел переход на страницу с пользовательским соглашением</t>
+    <t>Переход в раздел "Новости" через главное меню</t>
+  </si>
+  <si>
+    <t>2. В появившемся списке нажать на строку "Новости"</t>
+  </si>
+  <si>
+    <t>4. Страница "Новости"</t>
+  </si>
+  <si>
+    <t>4.1 Возможность перехода между страницами приложения</t>
   </si>
   <si>
     <t>ТС-021</t>
   </si>
   <si>
-    <t xml:space="preserve"> Работа кнопки "Назад"</t>
-  </si>
-  <si>
-    <t>3. На верхней панели нажать на иконку "Назад" (стрелка влево)</t>
-  </si>
-  <si>
-    <t>3. Произошел переход на предыдущую страницу приложения</t>
-  </si>
-  <si>
-    <t>4. Страница "Цитаты"</t>
+    <t>Пользователь успешно авторизован в приложении, открыта страница "Новости"</t>
   </si>
   <si>
     <t>ТС-022</t>
   </si>
   <si>
-    <t>Возможность развернуть для чтения цитату на выбор</t>
-  </si>
-  <si>
-    <t>Пользователь успешно авторизован в приложении, путем нажатии на иконку "Цитаты" перешел на страницу "Главное - жить любя"</t>
-  </si>
-  <si>
-    <t>1. Пролистать список цитат вниз, выбрать шестую сверху цитату и нажать на стрелочку над заголовком цитаты</t>
-  </si>
-  <si>
-    <t>1. В раскрывшемся окошке появляется текст выбранной цитаты</t>
+    <t>Переход на страницу "Цитаты" через кнопку на панели управления приложения</t>
   </si>
   <si>
     <t>ТС-023</t>
   </si>
   <si>
-    <t>2. Произошел переход на главную страницу приложения</t>
+    <t>Переход на страницу "Новости" через главное меню</t>
+  </si>
+  <si>
+    <t>2.Ссылка на страницу "Новости" не активна</t>
+  </si>
+  <si>
+    <t>5.2 Работа кнопок управления новостями (сотрировка, фильтр, обновление, создание новостей)</t>
   </si>
   <si>
     <t>ТС-024</t>
   </si>
   <si>
-    <t>Переход в раздел "Новости" через главное меню</t>
-  </si>
-  <si>
-    <t>2. В появившемся списке нажать на строку "Новости"</t>
+    <t>Работа кнопки "Фильтр"</t>
+  </si>
+  <si>
+    <t>1. На панели "Новости" нажать на иконку "Фильтры"</t>
+  </si>
+  <si>
+    <t>1. Произошел переход на страницу "Фильтрация новостей"</t>
   </si>
   <si>
     <t>ТС-025</t>
   </si>
   <si>
-    <t>5. Страница "Новости"</t>
-  </si>
-  <si>
-    <t>5.1 Возможность перехода между страницами приложения</t>
+    <t>Работа кнопки "Редактирование"</t>
+  </si>
+  <si>
+    <t>1. На панели "Новости" нажать на иконку "Редактирование"</t>
+  </si>
+  <si>
+    <t>1 Произошел переход на страницу управления новостями</t>
+  </si>
+  <si>
+    <t>6. Вкладка "Фильтровать новости" на странице "Новости"</t>
   </si>
   <si>
     <t>ТС-026</t>
   </si>
   <si>
-    <t>Пользователь успешно авторизован в приложении, открыта страница "Новости"</t>
+    <t>Все поля на странице "Фильтрация" новостей пустые</t>
+  </si>
+  <si>
+    <t>1. Нажать кнопку "Фильтр" на панели "Новости"</t>
+  </si>
+  <si>
+    <t>2. Оставит все поля пустыми и нажать кнопку "Фильтровать"</t>
   </si>
   <si>
     <t>ТС-027</t>
   </si>
   <si>
-    <t>Переход на страницу "О приложении" через главное меню</t>
+    <t>Выбор категории "Объявления" из выпадающего списка</t>
+  </si>
+  <si>
+    <t>2. В поле "Категория" из выпадающего меню выбрать строчку "Объявления" и нажать на нее</t>
+  </si>
+  <si>
+    <t>2. Выбрана категория "Обьявления"</t>
+  </si>
+  <si>
+    <t>3. Нажать кнопку "Фильтровать"</t>
+  </si>
+  <si>
+    <t>3. Произошел переход на страницу "Новости"</t>
   </si>
   <si>
     <t>ТС-028</t>
   </si>
   <si>
-    <t>Переход на страницу "Цитаты" через кнопку на панели управления приложения</t>
+    <t>Ввод категории новостей на кириллице с клавиатуры</t>
+  </si>
+  <si>
+    <t>2. В поле категория вручную ввести название категории "Праздник"</t>
+  </si>
+  <si>
+    <t>2. Название категории введено</t>
   </si>
   <si>
     <t>ТС-029</t>
   </si>
   <si>
-    <t>Переход на страницу "Новости" через главное меню</t>
-  </si>
-  <si>
-    <t>2.Ссылка на страницу "Новости" не активна</t>
-  </si>
-  <si>
-    <t>5.2 Работа кнопок управления новостями (сотрировка, фильтр, обновление, создание новостей)</t>
+    <t>Ввод названия категрии новостей цифрами с клавиатуры</t>
+  </si>
+  <si>
+    <t>2. В поле категория вручную ввести название категории цифрами</t>
+  </si>
+  <si>
+    <t>3. Переход на страницу "Новости" не осуществлен, появилось сообщение об ошибке - некорректном вооде названия категории</t>
   </si>
   <si>
     <t>ТС-030</t>
   </si>
   <si>
-    <t>Работа кнопки "Фильтр"</t>
-  </si>
-  <si>
-    <t>1. На панели "Новости" нажать на иконку "Фильтры"</t>
-  </si>
-  <si>
-    <t>1. Произошел переход на страницу "Фильтрация новостей"</t>
+    <t>Ввод названия категории новостей спец.символами</t>
+  </si>
+  <si>
+    <t>2. В поле категория вручную ввести название категории спец.символами</t>
   </si>
   <si>
     <t>ТС-031</t>
   </si>
   <si>
-    <t>Работа кнопки "Редактирование"</t>
-  </si>
-  <si>
-    <t>1. На панели "Новости" нажать на иконку "Редактирование"</t>
-  </si>
-  <si>
-    <t>1 Произошел переход на страницу управления новостями</t>
-  </si>
-  <si>
-    <t>6. Вкладка "Фильтровать новости" на странице "Новости"</t>
+    <t>Ввод названия категории новостей на латинице</t>
+  </si>
+  <si>
+    <t>2. В поле категория вручную ввести название категории на латинице</t>
   </si>
   <si>
     <t>ТС-032</t>
   </si>
   <si>
-    <t>Все поля на странице "Фильтрация" новостей пустые</t>
-  </si>
-  <si>
-    <t>1. Нажать кнопку "Фильтр" на панели "Новости"</t>
-  </si>
-  <si>
-    <t>2. Оставит все поля пустыми и нажать кнопку "Фильтровать"</t>
+    <t>Ввод названия категории новостей, отсутствующего в списке</t>
+  </si>
+  <si>
+    <t>2. В поле категория вручную ввести название категории "Информация о сотрудниках"</t>
   </si>
   <si>
     <t>ТС-033</t>
   </si>
   <si>
-    <t>Выбор категории "Объявления" из выпадающего списка</t>
-  </si>
-  <si>
-    <t>2. В поле "Категория" из выпадающего меню выбрать строчку "Объявления" и нажать на нее</t>
-  </si>
-  <si>
-    <t>2. Выбрана категория "Обявления"</t>
-  </si>
-  <si>
-    <t>3. Нажать кнопку "Фильтровать"</t>
-  </si>
-  <si>
-    <t>3. Произошел переход на страницу "Новости"</t>
+    <t>Заполнение только одного окна с датами - начальная дата</t>
+  </si>
+  <si>
+    <t>2. Ввести дату только в окно "Начало периода"</t>
+  </si>
+  <si>
+    <t>2. Дата введена</t>
+  </si>
+  <si>
+    <t>3. Кнопка "Фильтровать" активна, но переход на страницу "Новости" не осуществлен, появило сообщение об ошибке</t>
   </si>
   <si>
     <t>ТС-034</t>
   </si>
   <si>
-    <t>Ввод категории новостей на кириллице с клавиатуры</t>
-  </si>
-  <si>
-    <t>2. В поле категория вручную ввести название категории "Праздник"</t>
-  </si>
-  <si>
-    <t>2. Название категории введено</t>
+    <t>Заполнение только одного окна с датами - конечная дата</t>
+  </si>
+  <si>
+    <t>2. Ввести дату только в окно "Конец периода"</t>
   </si>
   <si>
     <t>ТС-035</t>
   </si>
   <si>
-    <t>Ввод названия категрии новостей цифрами с клавиатуры</t>
-  </si>
-  <si>
-    <t>2. В поле категория вручную ввести название категории цифрами</t>
-  </si>
-  <si>
-    <t>3. Переход на страницу "Новости" не осуществлен, появилось сообщение об ошибке - некорректном вооде названия категории</t>
+    <t>При заполнении дат указать конечную дату на несколько лет вперед, начальная дата - текущая</t>
+  </si>
+  <si>
+    <t>2. В поле "Начало периода" ввести текущую дату</t>
+  </si>
+  <si>
+    <t>3. В поле "Конец периода" ввести дату на несколько лет вперед 01.01.2078</t>
+  </si>
+  <si>
+    <t>3. Дата введена</t>
+  </si>
+  <si>
+    <t>4. Нажать кнопку "Фильтровать"</t>
+  </si>
+  <si>
+    <t>4. Кнопка "Фильтровать" активна, но появилось сообщение об ошибке</t>
   </si>
   <si>
     <t>ТС-036</t>
   </si>
   <si>
-    <t>Ввод названия категории новостей спец.символами</t>
-  </si>
-  <si>
-    <t>2. В поле категория вручную ввести название категории спец.символами</t>
+    <t>При заполнении дат указать начальную дату на несколько лет вперед, конечная дата - текущая</t>
+  </si>
+  <si>
+    <t>2. В поле "Начало периода" ввести дату на несколько лет вперед 31.12.2030</t>
   </si>
   <si>
     <t>ТС-037</t>
   </si>
   <si>
-    <t>Ввод названия категории новстей на латинице</t>
-  </si>
-  <si>
-    <t>2. В поле категория вручную ввести название категории на латинице</t>
+    <t xml:space="preserve"> Работа кнопки "Отмена"</t>
+  </si>
+  <si>
+    <t>2. Нажать кнопку "Отмена"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Вкладка "Панель управления" </t>
+  </si>
+  <si>
+    <t>7.1 Создание новостей</t>
   </si>
   <si>
     <t>ТС-038</t>
   </si>
   <si>
-    <t>Ввод названия категории новостей, отсутствующего в списке</t>
-  </si>
-  <si>
-    <t>2. В поле категория вручную ввести название категории "Информация о сотрудниках"</t>
+    <t>Создание активной новости с категорией "День рождения"</t>
+  </si>
+  <si>
+    <t>Пользователь успешно авторизован в приложении, открыл страницу "Новости" и нажал на кнопку "Редактирование"</t>
+  </si>
+  <si>
+    <t>1. На панели управления нажать кнопку "Добавить" (кружок с "плюсом")</t>
+  </si>
+  <si>
+    <t>1. Кнопка "Добаить" активна, произошел переход на страницу "Создание "Новости"</t>
+  </si>
+  <si>
+    <t>2. В поле "Категория" из выпадающего меню выбрать строчку "День рождения" и нажать на нее</t>
+  </si>
+  <si>
+    <t>2. Выбрана категория "День рождения"</t>
+  </si>
+  <si>
+    <t>3. Ввести текщую дату в поле "Дата"</t>
+  </si>
+  <si>
+    <t>4. Ввести текущее время в поле "Время"</t>
+  </si>
+  <si>
+    <t>4. Время введено</t>
+  </si>
+  <si>
+    <t>5. Заполнить поле "Заголовок"</t>
+  </si>
+  <si>
+    <t>5. Поле "Заголовок " заполнено</t>
+  </si>
+  <si>
+    <t>6. Выставить статус  новости "Активна"</t>
+  </si>
+  <si>
+    <t>6. Статус новости "Активна" выставлен</t>
+  </si>
+  <si>
+    <t>7. Нажать "Сохранить"</t>
+  </si>
+  <si>
+    <t>7. Произошел переход на вкладку "Панель управления", новость сохранена и появилась в списке</t>
   </si>
   <si>
     <t>ТС-039</t>
   </si>
   <si>
-    <t>Заполнение только одного окна с датами - начальная дата</t>
-  </si>
-  <si>
-    <t>2. Ввести дату только в окно "Начало периода"</t>
-  </si>
-  <si>
-    <t>2. Дата введена</t>
-  </si>
-  <si>
-    <t>3. Кнопка "Фильтровать" активна, но переход на страницу "Новости" не осуществлен, появило сообщение об ошибке</t>
+    <t>Создание не активной новости с категорией "Профсоюз"</t>
+  </si>
+  <si>
+    <t>2. В поле "Категория" из выпадающего меню выбрать строчку "Профсоюз" и нажать на нее</t>
+  </si>
+  <si>
+    <t>2. Выбрана категория "Профсоюз"</t>
+  </si>
+  <si>
+    <t>6. Выставить статус  новости "Не активна"</t>
+  </si>
+  <si>
+    <t>6. Статус новости "Не активна" выставлен</t>
   </si>
   <si>
     <t>ТС-040</t>
   </si>
   <si>
-    <t>Заполнение только одного окна с датами - конечная дата</t>
-  </si>
-  <si>
-    <t>2. Ввести дату только в окно "Конец периода"</t>
+    <t>Пустые поля при создании новости</t>
+  </si>
+  <si>
+    <t>2. Оставить все поля формы создания новости пустыми и нажать на кнопку "Сохранить"</t>
+  </si>
+  <si>
+    <t>2. Кнопка "Сохранить" активна, но создание новости не произошло, поля подсвечены красным, появлось сообщение об ошибке</t>
   </si>
   <si>
     <t>ТС-041</t>
   </si>
   <si>
-    <t>При заполнении дат указать конечную дату на несколько лет вперед, начальная дата - текущая</t>
-  </si>
-  <si>
-    <t>2. В поле "Начало периода" ввести текущую дату</t>
-  </si>
-  <si>
-    <t>3. В поле "Конец периода" ввести дату на несколько лет вперед 01.01.2078</t>
-  </si>
-  <si>
-    <t>3. Дата введена</t>
-  </si>
-  <si>
-    <t>4. Нажать кнопку "Фильтровать"</t>
-  </si>
-  <si>
-    <t>4. Кнопка "Фильтровать" активна, но появилось сообщение об ошибке</t>
+    <t>Ввод названия категории новостей вручную</t>
+  </si>
+  <si>
+    <t>2. Ввести вручную с клавиатуры в поле "Категория" название категории "Массаж"</t>
+  </si>
+  <si>
+    <t>3. Заполнить остальные поля</t>
+  </si>
+  <si>
+    <t>3. Остальные поля заполнены</t>
+  </si>
+  <si>
+    <t>4. Нажать кнопку "Сохранить"</t>
+  </si>
+  <si>
+    <t>4. Произошел переход на вкладку "Панель управления", новость сохранена и появилась в списке</t>
   </si>
   <si>
     <t>ТС-042</t>
   </si>
   <si>
-    <t>При заполнении дат указать начальную дату на несколько лет вперед, конечная дата - текущая</t>
-  </si>
-  <si>
-    <t>2. В поле "Начало периода" ввести дату на несколько лет вперед 31.12.2030</t>
+    <t>Ввод названия несуществующей в списке категории новостей</t>
+  </si>
+  <si>
+    <t>2.В меню "Категория" ввести название несуществующей категории ("Музыка")</t>
+  </si>
+  <si>
+    <t>2.Название категории введено</t>
+  </si>
+  <si>
+    <t>3. Ввести текст заголовка на латинице</t>
+  </si>
+  <si>
+    <t>3. Текст заголовка введен на латинице</t>
+  </si>
+  <si>
+    <t>4. Новость не сохранена, появлось сообщение об ошибке</t>
   </si>
   <si>
     <t>ТС-043</t>
   </si>
   <si>
-    <t xml:space="preserve"> Работа кнопки "Отмена"</t>
-  </si>
-  <si>
-    <t>2. Нажать кнопку "Отмена"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Вкладка "Панель управления" </t>
-  </si>
-  <si>
-    <t>7.1 Создание новостей</t>
+    <t>Ввод в строке "Заголовое" текста на латинице</t>
+  </si>
+  <si>
+    <t>2.В меню "Категория" выбрать любую категорию из списка ("Нужна помощь")</t>
+  </si>
+  <si>
+    <t>2. Категория выбрана</t>
   </si>
   <si>
     <t>ТС-044</t>
   </si>
   <si>
-    <t>Создание активной новости с категорией "День рождения"</t>
-  </si>
-  <si>
-    <t>Пользователь успешно авторизован в приложении, открыл страницу "Новости" и нажал на кнопку "Редактирование"</t>
-  </si>
-  <si>
-    <t>1. На панели управления нажать кнопку "Добавить" (кружок с "плюсом")</t>
-  </si>
-  <si>
-    <t>1. Кнопка "Добаить" активна, произошел переход на страницу "Создание "Новости"</t>
-  </si>
-  <si>
-    <t>2. В поле "Категория" из выпадающего меню выбрать строчку "День рождения" и нажать на нее</t>
-  </si>
-  <si>
-    <t>2. Выбрана категория "День рождения"</t>
-  </si>
-  <si>
-    <t>3. Ввести текщую дату в поле "Дата"</t>
-  </si>
-  <si>
-    <t>4. Ввести текущее время в поле "Время"</t>
-  </si>
-  <si>
-    <t>4. Время введено</t>
-  </si>
-  <si>
-    <t>5. Заполнить поле "Заголовок"</t>
-  </si>
-  <si>
-    <t>5. Поле "Заголовок " заполнено</t>
-  </si>
-  <si>
-    <t>6. Выставить статус  новости "Активна"</t>
-  </si>
-  <si>
-    <t>6. Статус новости "Активна" выставлен</t>
-  </si>
-  <si>
-    <t>7. Нажать "Сохранить"</t>
-  </si>
-  <si>
-    <t>7. Произошел переход на вкладку "Панель управления", новость сохранена и появилась в списке</t>
+    <t>Ввод в строке "Опсание" только цифр</t>
+  </si>
+  <si>
+    <t>3. Заполнить остальные поля (заголовок, дата, время)</t>
+  </si>
+  <si>
+    <t>3. Поля заполнены</t>
+  </si>
+  <si>
+    <t>4. В поле "Описание" ввести текст только цифры</t>
+  </si>
+  <si>
+    <t>4. В поле "Описание" введен текст только цифрами</t>
+  </si>
+  <si>
+    <t>5. Нажать кнопку "Сохранить"</t>
+  </si>
+  <si>
+    <t>5. Новость не сохранена, появлось сообщение об ошибке</t>
   </si>
   <si>
     <t>ТС-045</t>
   </si>
   <si>
-    <t>Создание не активной новости с категорией "Профсоюз"</t>
-  </si>
-  <si>
-    <t>2. В поле "Категория" из выпадающего меню выбрать строчку "Профсоюз" и нажать на нее</t>
-  </si>
-  <si>
-    <t>2. Выбрана категория "Профсоюз"</t>
-  </si>
-  <si>
-    <t>6. Выставить статус  новости "Не активна"</t>
-  </si>
-  <si>
-    <t>6. Статус новости "Не активна" выставлен</t>
+    <t>Ввод даты создания новости на 2 года вперед от текущей</t>
+  </si>
+  <si>
+    <t>3. В поле "Дата" ввести дату на 2 года вперед от текущей</t>
+  </si>
+  <si>
+    <t>4. Заполнить поля "Заголовок", "Время" и "Описание"</t>
+  </si>
+  <si>
+    <t>4. Поля заполнены</t>
   </si>
   <si>
     <t>ТС-046</t>
   </si>
   <si>
-    <t>Пустые поля при создании новости</t>
-  </si>
-  <si>
-    <t>2. Оставить все поля формы создания новости пустыми и нажать на кнопку "Сохранить"</t>
-  </si>
-  <si>
-    <t>2. Кнопка "Сохранить" активна, но создание новости не произошло, поля подсвечены красным, появлось сообщение об ошибке</t>
+    <t>Ввод времени создания новости используя "бегунок" на окружности циферблата</t>
+  </si>
+  <si>
+    <t>3. В поле "Время" "бегунком" на окружности циферблата выставить время публикации</t>
+  </si>
+  <si>
+    <t>3. Время выставлено</t>
+  </si>
+  <si>
+    <t>4. Заполнить поля "Заголовок", "Дата" и "Описание"</t>
+  </si>
+  <si>
+    <t>5. Произошел переход на вкладку "Панель управления", новость сохранена и появилась в списке</t>
   </si>
   <si>
     <t>ТС-047</t>
   </si>
   <si>
-    <t>Ввод названия категории новостей вручную</t>
-  </si>
-  <si>
-    <t>2. Ввести вручную с клавиатуры в поле "Категория" название категории "Массаж"</t>
-  </si>
-  <si>
-    <t>3. Заполнить остальные поля</t>
-  </si>
-  <si>
-    <t>3. Остальные поля заполнены</t>
-  </si>
-  <si>
-    <t>4. Нажать кнопку "Сохранить"</t>
-  </si>
-  <si>
-    <t>4. Произошел переход на вкладку "Панель управления", новость сохранена и появилась в списке</t>
+    <t>Ввод времени создания новости с клавиатуры</t>
+  </si>
+  <si>
+    <t>3. В поле "Время" с клавиатуры ввести время публикации</t>
+  </si>
+  <si>
+    <t>3. Время публикации введено</t>
   </si>
   <si>
     <t>ТС-048</t>
   </si>
   <si>
-    <t>Ввод названия несуществующей в списке категории новостей</t>
-  </si>
-  <si>
-    <t>2.В меню "Категория" ввести название несуществующей категории ("Музыка")</t>
-  </si>
-  <si>
-    <t>2.Название категории введено</t>
-  </si>
-  <si>
-    <t>3. Ввести текст заголовка на латинице</t>
-  </si>
-  <si>
-    <t>3. Текст заголовка введен на латинице</t>
-  </si>
-  <si>
-    <t>4. Новость не сохранена, появлось сообщение об ошибке</t>
+    <t>Ввод значений часов или минут, превышающих допустимые значения</t>
+  </si>
+  <si>
+    <t>3. В поле "Время" выбрать способ ввода с клавиатуры, ввести время публикации 33:58 и нажать "ОК"</t>
+  </si>
+  <si>
+    <t>3. Время введено, но появилось сообщение об ошибке, переход к другим полям не возможен до ввода корректных значений</t>
+  </si>
+  <si>
+    <t>7.2 Просмотр, сортировка, редактирование, удаление новостей</t>
   </si>
   <si>
     <t>ТС-049</t>
   </si>
   <si>
-    <t>Ввод в строке "Заголовое" текста на латинице</t>
-  </si>
-  <si>
-    <t>2.В меню "Категория" выбрать любую категорию из списка ("Нужна помощь")</t>
-  </si>
-  <si>
-    <t>2. Категория выбрана</t>
+    <t>Просмотр текста новости</t>
+  </si>
+  <si>
+    <t>1. Пролистать список новостей вниз, выбрать третью сверху новость и нажать на стрелочку в правом нижнем углу поля новости</t>
+  </si>
+  <si>
+    <t>1. В раскрывшемся окошке появляется текст выбранной новости</t>
   </si>
   <si>
     <t>ТС-050</t>
   </si>
   <si>
-    <t>Ввод в строке "Опсание" только цифр</t>
-  </si>
-  <si>
-    <t>3. Заполнить остальные поля (заголовок, дата, время)</t>
-  </si>
-  <si>
-    <t>3. Поля заполнены</t>
-  </si>
-  <si>
-    <t>4. В поле "Описание" ввести текст только цифры</t>
-  </si>
-  <si>
-    <t>4. В поле "Описание" введен текст только цифрами</t>
-  </si>
-  <si>
-    <t>5. Нажать кнопку "Сохранить"</t>
-  </si>
-  <si>
-    <t>5. Новость не сохранена, появлось сообщение об ошибке</t>
+    <t xml:space="preserve"> Редактирование новости</t>
+  </si>
+  <si>
+    <t>1. Пролистать список новостей вниз, выбрать пятую сверху новость и нажать на иконку "Редактировать"</t>
+  </si>
+  <si>
+    <t>1. Произошел переход на страницу "Редактирование Новости"</t>
+  </si>
+  <si>
+    <t>2. Отредактировать новость, внеся изменения в заголовок</t>
+  </si>
+  <si>
+    <t>2. Текст заголовка изменен</t>
+  </si>
+  <si>
+    <t>3. Нажать "Сохранить"</t>
+  </si>
+  <si>
+    <t>3. Произошел переход на вкладку "Панель управления", новость отредактирована</t>
   </si>
   <si>
     <t>ТС-051</t>
   </si>
   <si>
-    <t>Ввод даты создания новости на 2 года вперед от текущей</t>
-  </si>
-  <si>
-    <t>3. В поле "Дата" ввести дату на 2 года вперед от текущей</t>
-  </si>
-  <si>
-    <t>4. Заполнить поля "Заголовок", "Время" и "Описание"</t>
-  </si>
-  <si>
-    <t>4. Поля заполнены</t>
+    <t>Изменение статуса активной новости на "Не активна"</t>
+  </si>
+  <si>
+    <t>1. Пролистать список новостей вниз, выбрать любую активную новость и нажать на иконку "Редактировать"</t>
+  </si>
+  <si>
+    <t>2.Изменить статус новости, переключив "бегунок" в положение "Не активна"</t>
+  </si>
+  <si>
+    <t>2. Статус новости изменен</t>
+  </si>
+  <si>
+    <t>3. Произошел переход на вкладку "Панель управления", новость отредактирована, статус изменен на "Не активна"</t>
+  </si>
+  <si>
+    <t>7.3 Фильтрация новостей</t>
   </si>
   <si>
     <t>ТС-052</t>
   </si>
   <si>
-    <t>Ввод времени создания новости используя "бегунок" на окружности циферблата</t>
-  </si>
-  <si>
-    <t>3. В поле "Время" "бегунком" на окружности циферблата выставить время публикации</t>
-  </si>
-  <si>
-    <t>3. Время выставлено</t>
-  </si>
-  <si>
-    <t>4. Заполнить поля "Заголовок", "Дата" и "Описание"</t>
-  </si>
-  <si>
-    <t>5. Произошел переход на вкладку "Панель управления", новость сохранена и появилась в списке</t>
+    <t xml:space="preserve"> Фильтрация новостей по категории "Массаж" </t>
+  </si>
+  <si>
+    <t>1. На панели управления нажать кнопку "Фильтровать"</t>
+  </si>
+  <si>
+    <t>1. Кнопка "Фильтровать" активна, произошел переход на страницу "Фильтровать новости"</t>
+  </si>
+  <si>
+    <t>2. Из выпадающего списка выбрать категорию "Массаж"</t>
+  </si>
+  <si>
+    <t>3. Произошел перехо к списку новостей, новости отфильтрованы, на странице отображены только новости категории "Массаж"</t>
   </si>
   <si>
     <t>ТС-053</t>
   </si>
   <si>
-    <t>Ввод времени создания новости с клавиатуры</t>
-  </si>
-  <si>
-    <t>3. В поле "Время" с клавиатуры ввести время публикации</t>
-  </si>
-  <si>
-    <t>3. Время публикации введено</t>
+    <t>Заполнен чек-бокс статуса "Активна"</t>
+  </si>
+  <si>
+    <t>2. Оставить заполненным только чек-бокс статуса "Активна"</t>
+  </si>
+  <si>
+    <t>2. Чек-бокс заполнен</t>
+  </si>
+  <si>
+    <t>3. Произошел перехо к списку новостей, новости отфильтрованы, на странице отображены только новости в статусе "Активна"</t>
   </si>
   <si>
     <t>ТС-054</t>
   </si>
   <si>
-    <t>Ввод значений часов или минут, превышающих допустимые значения</t>
-  </si>
-  <si>
-    <t>3. В поле "Время" выбрать способ ввода с клавиатуры, ввести время публикации 33:58 и нажать "ОК"</t>
-  </si>
-  <si>
-    <t>3. Время введено, но появилось сообщение об ошибке, переход к другим полям не возможен до ввода корректных значений</t>
-  </si>
-  <si>
-    <t>7.2 Просмотр, сортировка, редактирование, удаление новостей</t>
+    <t>Заполнен чек-бокс статуса "Не активна"</t>
+  </si>
+  <si>
+    <t>2. Оставить заполненным только чек-бокс статуса "Не активна"</t>
+  </si>
+  <si>
+    <t>3. Произошел перехо к списку новостей, новости отфильтрованы, на странице отображены только новости в статусе "Не активна"</t>
   </si>
   <si>
     <t>ТС-055</t>
-  </si>
-  <si>
-    <t>Просмотр текста новости</t>
-  </si>
-  <si>
-    <t>1. Пролистать список новостей вниз, выбрать третью сверху новость и нажать на стрелочку в правом нижнем углу поля новости</t>
-  </si>
-  <si>
-    <t>1. В раскрывшемся окошке появляется текст выбранной новости</t>
-  </si>
-  <si>
-    <t>ТС-056</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Редактирование новости</t>
-  </si>
-  <si>
-    <t>1. Пролистать список новостей вниз, выбрать пятую сверху новость и нажать на иконку "Редактировать"</t>
-  </si>
-  <si>
-    <t>1. Произошел переход на страницу "Редактирование Новости"</t>
-  </si>
-  <si>
-    <t>2. Отредактировать новость, внеся изменения в заголовок</t>
-  </si>
-  <si>
-    <t>2. Текст заголовка изменен</t>
-  </si>
-  <si>
-    <t>3. Нажать "Сохранить"</t>
-  </si>
-  <si>
-    <t>3. Произошел переход на вкладку "Панель управления", новость отредактирована</t>
-  </si>
-  <si>
-    <t>ТС-057</t>
-  </si>
-  <si>
-    <t>Изменение статуса активной новости на "Не активна"</t>
-  </si>
-  <si>
-    <t>1. Пролистать список новостей вниз, выбрать любую активную новость и нажать на иконку "Редактировать"</t>
-  </si>
-  <si>
-    <t>2.Изменить статус новости, переключив "бегунок" в положение "Не активна"</t>
-  </si>
-  <si>
-    <t>2. Статус новости изменен</t>
-  </si>
-  <si>
-    <t>3. Произошел переход на вкладку "Панель управления", новость отредактирована, статус изменен на "Не активна"</t>
-  </si>
-  <si>
-    <t>7.3 Фильтрация новостей</t>
-  </si>
-  <si>
-    <t>ТС-058</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Фильтрация новостей по категории "Массаж" </t>
-  </si>
-  <si>
-    <t>1. На панели управления нажать кнопку "Фильтровать"</t>
-  </si>
-  <si>
-    <t>1. Кнопка "Фильтровать" активна, произошел переход на страницу "Фильтровать новости"</t>
-  </si>
-  <si>
-    <t>2. Из выпадающего списка выбрать категорию "Массаж"</t>
-  </si>
-  <si>
-    <t>3. Произошел перехо к списку новостей, новости отфильтрованы, на странице отображены только новости категории "Массаж"</t>
-  </si>
-  <si>
-    <t>ТС-059</t>
-  </si>
-  <si>
-    <t>Заполнен чек-бокс статуса "Активна"</t>
-  </si>
-  <si>
-    <t>2. Оставить заполненным только чек-бокс статуса "Активна"</t>
-  </si>
-  <si>
-    <t>2. Чек-бокс заполнен</t>
-  </si>
-  <si>
-    <t>3. Произошел перехо к списку новостей, новости отфильтрованы, на странице отображены только новости в статусе "Активна"</t>
-  </si>
-  <si>
-    <t>ТС-060</t>
-  </si>
-  <si>
-    <t>Заполнен чек-бокс статуса "Не активна"</t>
-  </si>
-  <si>
-    <t>2. Оставить заполненным только чек-бокс статуса "Не активна"</t>
-  </si>
-  <si>
-    <t>3. Произошел перехо к списку новостей, новости отфильтрованы, на странице отображены только новости в статусе "Не активна"</t>
-  </si>
-  <si>
-    <t>ТС-061</t>
   </si>
   <si>
     <t>Работа кнопки "Отмена"</t>
@@ -1034,7 +971,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="36">
     <border/>
     <border>
       <left style="thin">
@@ -1284,17 +1221,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -1384,17 +1310,6 @@
       <bottom/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1404,6 +1319,17 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1527,8 +1453,11 @@
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="21" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1539,22 +1468,13 @@
     <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="22" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="24" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="26" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1562,21 +1482,21 @@
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="27" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="26" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="27" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="28" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="30" fillId="3" fontId="4" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="29" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="31" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="32" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="33" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="34" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1587,17 +1507,20 @@
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1605,10 +1528,13 @@
     <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="35" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="33" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="36" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="35" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2661,15 +2587,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" ht="51.0" customHeight="1">
-      <c r="A54" s="28" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="27" t="s">
+      <c r="C54" s="10"/>
+      <c r="D54" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="29" t="s">
@@ -2684,9 +2610,9 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="24"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="9"/>
       <c r="E55" s="16"/>
       <c r="F55" s="14" t="s">
         <v>104</v>
@@ -2695,299 +2621,472 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="28" t="s">
+    <row r="56" ht="38.25" customHeight="1">
+      <c r="A56" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="9" t="s">
+      <c r="C56" s="40"/>
+      <c r="D56" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="F56" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="G56" s="23" t="s">
+      <c r="F56" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="45"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="20"/>
+      <c r="D58" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" ht="33.75" customHeight="1">
+      <c r="A59" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="29"/>
+      <c r="D59" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G59" s="21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="24"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G57" s="23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="58" ht="38.25" customHeight="1">
-      <c r="A58" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="B58" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="C58" s="39"/>
-      <c r="D58" s="40" t="s">
+    <row r="60" ht="33.75" customHeight="1">
+      <c r="A60" s="24"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G60" s="23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" ht="32.25" customHeight="1">
+      <c r="A61" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="G58" s="34" t="s">
+      <c r="E61" s="29" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="8"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="C60" s="37"/>
-      <c r="D60" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="F60" s="20" t="s">
+      <c r="F61" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G60" s="21" t="s">
+      <c r="G61" s="21" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="22"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G61" s="23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" ht="32.25" customHeight="1">
       <c r="A62" s="24"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
       <c r="F62" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="63" ht="38.25" customHeight="1">
-      <c r="A63" s="28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" s="50"/>
+      <c r="C63" s="50"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="51"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="B64" s="53"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="54"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="24"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G66" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="58"/>
+      <c r="D67" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G67" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+    </row>
+    <row r="68" ht="38.25" customHeight="1">
+      <c r="A68" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" s="29"/>
+      <c r="D68" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G68" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="31"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="C63" s="29"/>
-      <c r="D63" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="G63" s="42" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="22"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G64" s="23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="24"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="28" t="s">
+      <c r="G69" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71" s="61"/>
+      <c r="D71" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="B66" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="29"/>
-      <c r="D66" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E66" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="G66" s="42" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="22"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="31"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="G68" s="44" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="B69" s="46"/>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="47"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="48" t="s">
-        <v>129</v>
-      </c>
-      <c r="B70" s="49" t="s">
-        <v>130</v>
-      </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="G70" s="21" t="s">
+      <c r="F71" s="20" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="71" ht="33.75" customHeight="1">
-      <c r="A71" s="28" t="s">
+      <c r="G71" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="27" t="s">
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="4"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="40"/>
+      <c r="D72" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E71" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="F71" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G71" s="21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="72" ht="33.75" customHeight="1">
-      <c r="A72" s="24"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G72" s="23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="73" ht="32.25" customHeight="1">
-      <c r="A73" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="B73" s="29" t="s">
+      <c r="E72" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="F72" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C73" s="27"/>
-      <c r="D73" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="F73" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G73" s="21" t="s">
-        <v>99</v>
-      </c>
+      <c r="G72" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="4"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="8"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
@@ -3008,94 +3107,201 @@
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
     </row>
-    <row r="74" ht="32.25" customHeight="1">
-      <c r="A74" s="24"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G74" s="23" t="s">
+    <row r="74" ht="23.25" customHeight="1">
+      <c r="A74" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="37"/>
+      <c r="D74" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+    </row>
+    <row r="75" ht="23.25" customHeight="1">
+      <c r="A75" s="24"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G75" s="23" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="75" ht="39.75" customHeight="1">
-      <c r="A75" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="B75" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C75" s="29"/>
-      <c r="D75" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E75" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="F75" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G75" s="21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="76" ht="39.75" customHeight="1">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="G76" s="34" t="s">
-        <v>105</v>
-      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+    </row>
+    <row r="76" ht="38.25" customHeight="1">
+      <c r="A76" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="29"/>
+      <c r="D76" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="B77" s="52"/>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="53"/>
+      <c r="A77" s="22"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G77" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="54" t="s">
-        <v>141</v>
-      </c>
-      <c r="B78" s="55"/>
-      <c r="C78" s="55"/>
-      <c r="D78" s="55"/>
-      <c r="E78" s="55"/>
-      <c r="F78" s="55"/>
-      <c r="G78" s="56"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="36" t="s">
+      <c r="A78" s="24"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G78" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+    </row>
+    <row r="79" ht="25.5" customHeight="1">
+      <c r="A79" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C79" s="29"/>
+      <c r="D79" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F79" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B79" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="C79" s="19"/>
-      <c r="D79" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="F79" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>99</v>
+      <c r="G79" s="23" t="s">
+        <v>134</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -3118,16 +3324,16 @@
       <c r="Z79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="24"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
+      <c r="A80" s="22"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
       <c r="F80" s="14" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="G80" s="23" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -3150,24 +3356,16 @@
       <c r="Z80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="B81" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="C81" s="29"/>
-      <c r="D81" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F81" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G81" s="21" t="s">
-        <v>99</v>
+      <c r="A81" s="24"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G81" s="23" t="s">
+        <v>149</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
@@ -3190,16 +3388,24 @@
       <c r="Z81" s="4"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="22"/>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G82" s="57" t="s">
-        <v>105</v>
+      <c r="A82" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C82" s="29"/>
+      <c r="D82" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G82" s="23" t="s">
+        <v>134</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
@@ -3222,24 +3428,16 @@
       <c r="Z82" s="4"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="B83" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="C83" s="60"/>
-      <c r="D83" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="59" t="s">
-        <v>143</v>
-      </c>
+      <c r="A83" s="22"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
       <c r="F83" s="14" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="G83" s="23" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
@@ -3261,25 +3459,17 @@
       <c r="Y83" s="4"/>
       <c r="Z83" s="4"/>
     </row>
-    <row r="84" ht="38.25" customHeight="1">
-      <c r="A84" s="28" t="s">
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="24"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B84" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="C84" s="29"/>
-      <c r="D84" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F84" s="14" t="s">
-        <v>98</v>
-      </c>
       <c r="G84" s="23" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
@@ -3301,17 +3491,25 @@
       <c r="Y84" s="4"/>
       <c r="Z84" s="4"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="31"/>
-      <c r="B85" s="32"/>
-      <c r="C85" s="32"/>
-      <c r="D85" s="32"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="G85" s="34" t="s">
-        <v>150</v>
+    <row r="85" ht="25.5" customHeight="1">
+      <c r="A85" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B85" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="29"/>
+      <c r="D85" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G85" s="23" t="s">
+        <v>134</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
@@ -3334,15 +3532,17 @@
       <c r="Z85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="8"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G86" s="23" t="s">
+        <v>153</v>
+      </c>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
@@ -3364,538 +3564,239 @@
       <c r="Z86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="62" t="s">
-        <v>152</v>
-      </c>
-      <c r="B87" s="49" t="s">
+      <c r="A87" s="24"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G87" s="23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="88" ht="25.5" customHeight="1">
+      <c r="A88" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="B88" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="29"/>
+      <c r="D88" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F88" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G88" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="22"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G89" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="C87" s="63"/>
-      <c r="D87" s="50" t="s">
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="24"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G90" s="23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="91" ht="38.25" customHeight="1">
+      <c r="A91" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="B91" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="29"/>
+      <c r="D91" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E87" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="F87" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="G87" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
-      <c r="X87" s="4"/>
-      <c r="Y87" s="4"/>
-      <c r="Z87" s="4"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="B88" s="41" t="s">
+      <c r="E91" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F91" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G91" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="22"/>
+      <c r="B92" s="13"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G92" s="23" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="24"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G93" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C88" s="39"/>
-      <c r="D88" s="40" t="s">
+    </row>
+    <row r="94" ht="25.5" customHeight="1">
+      <c r="A94" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B94" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C94" s="29"/>
+      <c r="D94" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E88" s="65" t="s">
-        <v>143</v>
-      </c>
-      <c r="F88" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="G88" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="4"/>
-      <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
-      <c r="Z88" s="4"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
-      <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
-      <c r="Z89" s="4"/>
-    </row>
-    <row r="90" ht="23.25" customHeight="1">
-      <c r="A90" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="B90" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="C90" s="37"/>
-      <c r="D90" s="19" t="s">
+      <c r="E94" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G94" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="22"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G95" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="24"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G96" s="23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C97" s="29"/>
+      <c r="D97" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E90" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="F90" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="G90" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4"/>
-      <c r="W90" s="4"/>
-      <c r="X90" s="4"/>
-      <c r="Y90" s="4"/>
-      <c r="Z90" s="4"/>
-    </row>
-    <row r="91" ht="23.25" customHeight="1">
-      <c r="A91" s="24"/>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G91" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
-      <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
-      <c r="Z91" s="4"/>
-    </row>
-    <row r="92" ht="38.25" customHeight="1">
-      <c r="A92" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B92" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="C92" s="29"/>
-      <c r="D92" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F92" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G92" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-      <c r="Z92" s="4"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="22"/>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="G93" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-      <c r="Z93" s="4"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="24"/>
-      <c r="B94" s="16"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="16"/>
-      <c r="E94" s="16"/>
-      <c r="F94" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G94" s="23" t="s">
+      <c r="E97" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F97" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G97" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="22"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G98" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="4"/>
-      <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
-      <c r="Z94" s="4"/>
-    </row>
-    <row r="95" ht="25.5" customHeight="1">
-      <c r="A95" s="28" t="s">
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="24"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G99" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="B95" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="C95" s="29"/>
-      <c r="D95" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F95" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G95" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
-      <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
-      <c r="Z95" s="4"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="22"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="G96" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="4"/>
-      <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-      <c r="Z96" s="4"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="24"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
-      <c r="E97" s="16"/>
-      <c r="F97" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G97" s="23" t="s">
+    </row>
+    <row r="100" ht="51.0" customHeight="1">
+      <c r="A100" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="B100" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" s="29"/>
+      <c r="D100" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E100" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G100" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="22"/>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G101" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-      <c r="V97" s="4"/>
-      <c r="W97" s="4"/>
-      <c r="X97" s="4"/>
-      <c r="Y97" s="4"/>
-      <c r="Z97" s="4"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="B98" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="C98" s="29"/>
-      <c r="D98" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F98" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G98" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4"/>
-      <c r="S98" s="4"/>
-      <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
-      <c r="V98" s="4"/>
-      <c r="W98" s="4"/>
-      <c r="X98" s="4"/>
-      <c r="Y98" s="4"/>
-      <c r="Z98" s="4"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="22"/>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="G99" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-      <c r="V99" s="4"/>
-      <c r="W99" s="4"/>
-      <c r="X99" s="4"/>
-      <c r="Y99" s="4"/>
-      <c r="Z99" s="4"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="24"/>
-      <c r="B100" s="16"/>
-      <c r="C100" s="16"/>
-      <c r="D100" s="16"/>
-      <c r="E100" s="16"/>
-      <c r="F100" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G100" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
-      <c r="S100" s="4"/>
-      <c r="T100" s="4"/>
-      <c r="U100" s="4"/>
-      <c r="V100" s="4"/>
-      <c r="W100" s="4"/>
-      <c r="X100" s="4"/>
-      <c r="Y100" s="4"/>
-      <c r="Z100" s="4"/>
-    </row>
-    <row r="101" ht="25.5" customHeight="1">
-      <c r="A101" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B101" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="C101" s="29"/>
-      <c r="D101" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F101" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G101" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-      <c r="V101" s="4"/>
-      <c r="W101" s="4"/>
-      <c r="X101" s="4"/>
-      <c r="Y101" s="4"/>
-      <c r="Z101" s="4"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="22"/>
@@ -3904,30 +3805,11 @@
       <c r="D102" s="13"/>
       <c r="E102" s="13"/>
       <c r="F102" s="14" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G102" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-      <c r="V102" s="4"/>
-      <c r="W102" s="4"/>
-      <c r="X102" s="4"/>
-      <c r="Y102" s="4"/>
-      <c r="Z102" s="4"/>
+        <v>179</v>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="24"/>
@@ -3936,14 +3818,14 @@
       <c r="D103" s="16"/>
       <c r="E103" s="16"/>
       <c r="F103" s="14" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="G103" s="23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="104" ht="25.5" customHeight="1">
-      <c r="A104" s="28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="38" t="s">
         <v>182</v>
       </c>
       <c r="B104" s="29" t="s">
@@ -3951,16 +3833,16 @@
       </c>
       <c r="C104" s="29"/>
       <c r="D104" s="27" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E104" s="29" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="G104" s="23" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
@@ -3973,135 +3855,123 @@
         <v>184</v>
       </c>
       <c r="G105" s="23" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="24"/>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16"/>
-      <c r="D106" s="16"/>
-      <c r="E106" s="16"/>
+      <c r="A106" s="22"/>
+      <c r="B106" s="13"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="13"/>
+      <c r="E106" s="13"/>
       <c r="F106" s="14" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G106" s="23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="107" ht="38.25" customHeight="1">
-      <c r="A107" s="28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="24"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="G107" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="108" ht="21.75" customHeight="1">
+      <c r="A108" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="B107" s="29" t="s">
+      <c r="B108" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="C107" s="29"/>
-      <c r="D107" s="27" t="s">
+      <c r="C108" s="29"/>
+      <c r="D108" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E107" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F107" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G107" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="22"/>
-      <c r="B108" s="13"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
+      <c r="E108" s="29" t="s">
+        <v>124</v>
+      </c>
       <c r="F108" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G108" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="109" ht="21.75" customHeight="1">
+      <c r="A109" s="31"/>
+      <c r="B109" s="32"/>
+      <c r="C109" s="32"/>
+      <c r="D109" s="32"/>
+      <c r="E109" s="32"/>
+      <c r="F109" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="G108" s="23" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="24"/>
-      <c r="B109" s="16"/>
-      <c r="C109" s="16"/>
-      <c r="D109" s="16"/>
-      <c r="E109" s="16"/>
-      <c r="F109" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G109" s="23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="110" ht="25.5" customHeight="1">
-      <c r="A110" s="28" t="s">
+      <c r="G109" s="34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="B110" s="29" t="s">
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="8"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="C110" s="29"/>
-      <c r="D110" s="27" t="s">
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="8"/>
+    </row>
+    <row r="112" ht="63.75" customHeight="1">
+      <c r="A112" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="B112" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C112" s="37"/>
+      <c r="D112" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E110" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F110" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G110" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="22"/>
-      <c r="B111" s="13"/>
-      <c r="C111" s="13"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
-      <c r="F111" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="G111" s="23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="24"/>
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
-      <c r="D112" s="16"/>
-      <c r="E112" s="16"/>
-      <c r="F112" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G112" s="23" t="s">
+      <c r="E112" s="37" t="s">
         <v>192</v>
       </c>
+      <c r="F112" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="G112" s="21" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="B113" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="C113" s="29"/>
-      <c r="D113" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E113" s="29" t="s">
-        <v>143</v>
-      </c>
+      <c r="A113" s="22"/>
+      <c r="B113" s="13"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
       <c r="F113" s="14" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="G113" s="23" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
@@ -4110,46 +3980,95 @@
       <c r="C114" s="13"/>
       <c r="D114" s="13"/>
       <c r="E114" s="13"/>
-      <c r="F114" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="G114" s="23" t="s">
-        <v>191</v>
-      </c>
+      <c r="F114" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="G114" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4"/>
+      <c r="S114" s="4"/>
+      <c r="T114" s="4"/>
+      <c r="U114" s="4"/>
+      <c r="V114" s="4"/>
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="4"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="24"/>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
+      <c r="A115" s="22"/>
+      <c r="B115" s="13"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
       <c r="F115" s="14" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="116" ht="51.0" customHeight="1">
-      <c r="A116" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="B116" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="C116" s="29"/>
-      <c r="D116" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E116" s="29" t="s">
-        <v>143</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="4"/>
+      <c r="T115" s="4"/>
+      <c r="U115" s="4"/>
+      <c r="V115" s="4"/>
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="4"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="22"/>
+      <c r="B116" s="13"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="13"/>
+      <c r="E116" s="13"/>
       <c r="F116" s="14" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>155</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4"/>
+      <c r="S116" s="4"/>
+      <c r="T116" s="4"/>
+      <c r="U116" s="4"/>
+      <c r="V116" s="4"/>
+      <c r="W116" s="4"/>
+      <c r="X116" s="4"/>
+      <c r="Y116" s="4"/>
+      <c r="Z116" s="4"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="22"/>
@@ -4158,58 +4077,134 @@
       <c r="D117" s="13"/>
       <c r="E117" s="13"/>
       <c r="F117" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>191</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="4"/>
+      <c r="R117" s="4"/>
+      <c r="S117" s="4"/>
+      <c r="T117" s="4"/>
+      <c r="U117" s="4"/>
+      <c r="V117" s="4"/>
+      <c r="W117" s="4"/>
+      <c r="X117" s="4"/>
+      <c r="Y117" s="4"/>
+      <c r="Z117" s="4"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="22"/>
-      <c r="B118" s="13"/>
-      <c r="C118" s="13"/>
-      <c r="D118" s="13"/>
+      <c r="A118" s="24"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16"/>
       <c r="E118" s="13"/>
       <c r="F118" s="14" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>200</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="4"/>
+      <c r="S118" s="4"/>
+      <c r="T118" s="4"/>
+      <c r="U118" s="4"/>
+      <c r="V118" s="4"/>
+      <c r="W118" s="4"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="4"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="24"/>
-      <c r="B119" s="16"/>
-      <c r="C119" s="16"/>
-      <c r="D119" s="16"/>
-      <c r="E119" s="16"/>
-      <c r="F119" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="G119" s="23" t="s">
-        <v>202</v>
-      </c>
+      <c r="A119" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C119" s="29"/>
+      <c r="D119" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G119" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4"/>
+      <c r="S119" s="4"/>
+      <c r="T119" s="4"/>
+      <c r="U119" s="4"/>
+      <c r="V119" s="4"/>
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B120" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="C120" s="29"/>
-      <c r="D120" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E120" s="29" t="s">
-        <v>143</v>
-      </c>
+      <c r="A120" s="22"/>
+      <c r="B120" s="13"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
       <c r="F120" s="14" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="G120" s="23" t="s">
-        <v>155</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+      <c r="P120" s="4"/>
+      <c r="Q120" s="4"/>
+      <c r="R120" s="4"/>
+      <c r="S120" s="4"/>
+      <c r="T120" s="4"/>
+      <c r="U120" s="4"/>
+      <c r="V120" s="4"/>
+      <c r="W120" s="4"/>
+      <c r="X120" s="4"/>
+      <c r="Y120" s="4"/>
+      <c r="Z120" s="4"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="22"/>
@@ -4217,12 +4212,31 @@
       <c r="C121" s="13"/>
       <c r="D121" s="13"/>
       <c r="E121" s="13"/>
-      <c r="F121" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="G121" s="23" t="s">
-        <v>191</v>
-      </c>
+      <c r="F121" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="G121" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="4"/>
+      <c r="R121" s="4"/>
+      <c r="S121" s="4"/>
+      <c r="T121" s="4"/>
+      <c r="U121" s="4"/>
+      <c r="V121" s="4"/>
+      <c r="W121" s="4"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
+      <c r="Z121" s="4"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="22"/>
@@ -4231,101 +4245,238 @@
       <c r="D122" s="13"/>
       <c r="E122" s="13"/>
       <c r="F122" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="G122" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="G122" s="23" t="s">
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="4"/>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="4"/>
+      <c r="R122" s="4"/>
+      <c r="S122" s="4"/>
+      <c r="T122" s="4"/>
+      <c r="U122" s="4"/>
+      <c r="V122" s="4"/>
+      <c r="W122" s="4"/>
+      <c r="X122" s="4"/>
+      <c r="Y122" s="4"/>
+      <c r="Z122" s="4"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="22"/>
+      <c r="B123" s="13"/>
+      <c r="C123" s="13"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="14" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="24"/>
-      <c r="B123" s="16"/>
-      <c r="C123" s="16"/>
-      <c r="D123" s="16"/>
-      <c r="E123" s="16"/>
-      <c r="F123" s="14" t="s">
+      <c r="G123" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="G123" s="23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="124" ht="21.75" customHeight="1">
-      <c r="A124" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="B124" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C124" s="29"/>
-      <c r="D124" s="27" t="s">
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="4"/>
+      <c r="S123" s="4"/>
+      <c r="T123" s="4"/>
+      <c r="U123" s="4"/>
+      <c r="V123" s="4"/>
+      <c r="W123" s="4"/>
+      <c r="X123" s="4"/>
+      <c r="Y123" s="4"/>
+      <c r="Z123" s="4"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="22"/>
+      <c r="B124" s="13"/>
+      <c r="C124" s="13"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="G124" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4"/>
+      <c r="S124" s="4"/>
+      <c r="T124" s="4"/>
+      <c r="U124" s="4"/>
+      <c r="V124" s="4"/>
+      <c r="W124" s="4"/>
+      <c r="X124" s="4"/>
+      <c r="Y124" s="4"/>
+      <c r="Z124" s="4"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="24"/>
+      <c r="B125" s="16"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="16"/>
+      <c r="F125" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="G125" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="H125" s="4"/>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+      <c r="L125" s="4"/>
+      <c r="M125" s="4"/>
+      <c r="N125" s="4"/>
+      <c r="O125" s="4"/>
+      <c r="P125" s="4"/>
+      <c r="Q125" s="4"/>
+      <c r="R125" s="4"/>
+      <c r="S125" s="4"/>
+      <c r="T125" s="4"/>
+      <c r="U125" s="4"/>
+      <c r="V125" s="4"/>
+      <c r="W125" s="4"/>
+      <c r="X125" s="4"/>
+      <c r="Y125" s="4"/>
+      <c r="Z125" s="4"/>
+    </row>
+    <row r="126" ht="25.5" customHeight="1">
+      <c r="A126" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B126" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="C126" s="29"/>
+      <c r="D126" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E124" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F124" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G124" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="125" ht="21.75" customHeight="1">
-      <c r="A125" s="31"/>
-      <c r="B125" s="32"/>
-      <c r="C125" s="32"/>
-      <c r="D125" s="32"/>
-      <c r="E125" s="32"/>
-      <c r="F125" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="G125" s="34" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="8"/>
+      <c r="E126" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G126" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+      <c r="L126" s="4"/>
+      <c r="M126" s="4"/>
+      <c r="N126" s="4"/>
+      <c r="O126" s="4"/>
+      <c r="P126" s="4"/>
+      <c r="Q126" s="4"/>
+      <c r="R126" s="4"/>
+      <c r="S126" s="4"/>
+      <c r="T126" s="4"/>
+      <c r="U126" s="4"/>
+      <c r="V126" s="4"/>
+      <c r="W126" s="4"/>
+      <c r="X126" s="4"/>
+      <c r="Y126" s="4"/>
+      <c r="Z126" s="4"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="8"/>
-    </row>
-    <row r="128" ht="63.75" customHeight="1">
-      <c r="A128" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="B128" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="C128" s="37"/>
-      <c r="D128" s="19" t="s">
+      <c r="A127" s="24"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="G127" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="H127" s="4"/>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+      <c r="L127" s="4"/>
+      <c r="M127" s="4"/>
+      <c r="N127" s="4"/>
+      <c r="O127" s="4"/>
+      <c r="P127" s="4"/>
+      <c r="Q127" s="4"/>
+      <c r="R127" s="4"/>
+      <c r="S127" s="4"/>
+      <c r="T127" s="4"/>
+      <c r="U127" s="4"/>
+      <c r="V127" s="4"/>
+      <c r="W127" s="4"/>
+      <c r="X127" s="4"/>
+      <c r="Y127" s="4"/>
+      <c r="Z127" s="4"/>
+    </row>
+    <row r="128" ht="25.5" customHeight="1">
+      <c r="A128" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="B128" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="C128" s="29"/>
+      <c r="D128" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E128" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="F128" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G128" s="21" t="s">
-        <v>215</v>
-      </c>
+      <c r="E128" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G128" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="H128" s="4"/>
+      <c r="I128" s="4"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="4"/>
+      <c r="L128" s="4"/>
+      <c r="M128" s="4"/>
+      <c r="N128" s="4"/>
+      <c r="O128" s="4"/>
+      <c r="P128" s="4"/>
+      <c r="Q128" s="4"/>
+      <c r="R128" s="4"/>
+      <c r="S128" s="4"/>
+      <c r="T128" s="4"/>
+      <c r="U128" s="4"/>
+      <c r="V128" s="4"/>
+      <c r="W128" s="4"/>
+      <c r="X128" s="4"/>
+      <c r="Y128" s="4"/>
+      <c r="Z128" s="4"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="22"/>
@@ -4334,11 +4485,30 @@
       <c r="D129" s="13"/>
       <c r="E129" s="13"/>
       <c r="F129" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G129" s="23" t="s">
-        <v>217</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="4"/>
+      <c r="R129" s="4"/>
+      <c r="S129" s="4"/>
+      <c r="T129" s="4"/>
+      <c r="U129" s="4"/>
+      <c r="V129" s="4"/>
+      <c r="W129" s="4"/>
+      <c r="X129" s="4"/>
+      <c r="Y129" s="4"/>
+      <c r="Z129" s="4"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="22"/>
@@ -4346,11 +4516,11 @@
       <c r="C130" s="13"/>
       <c r="D130" s="13"/>
       <c r="E130" s="13"/>
-      <c r="F130" s="66" t="s">
-        <v>218</v>
-      </c>
-      <c r="G130" s="67" t="s">
-        <v>200</v>
+      <c r="F130" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G130" s="23" t="s">
+        <v>220</v>
       </c>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
@@ -4373,16 +4543,16 @@
       <c r="Z130" s="4"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="22"/>
-      <c r="B131" s="13"/>
-      <c r="C131" s="13"/>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
+      <c r="A131" s="24"/>
+      <c r="B131" s="16"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
       <c r="F131" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G131" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
@@ -4405,16 +4575,24 @@
       <c r="Z131" s="4"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="22"/>
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
-      <c r="F132" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="G132" s="23" t="s">
-        <v>222</v>
+      <c r="A132" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="B132" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C132" s="29"/>
+      <c r="D132" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G132" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
@@ -4443,10 +4621,10 @@
       <c r="D133" s="13"/>
       <c r="E133" s="13"/>
       <c r="F133" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G133" s="23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
@@ -4469,16 +4647,16 @@
       <c r="Z133" s="4"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="24"/>
-      <c r="B134" s="16"/>
-      <c r="C134" s="16"/>
-      <c r="D134" s="16"/>
+      <c r="A134" s="22"/>
+      <c r="B134" s="13"/>
+      <c r="C134" s="13"/>
+      <c r="D134" s="13"/>
       <c r="E134" s="13"/>
       <c r="F134" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G134" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
@@ -4501,24 +4679,16 @@
       <c r="Z134" s="4"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="B135" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="C135" s="29"/>
-      <c r="D135" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E135" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F135" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G135" s="42" t="s">
-        <v>215</v>
+      <c r="A135" s="24"/>
+      <c r="B135" s="16"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="16"/>
+      <c r="F135" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="G135" s="23" t="s">
+        <v>229</v>
       </c>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
@@ -4541,16 +4711,24 @@
       <c r="Z135" s="4"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="22"/>
-      <c r="B136" s="13"/>
-      <c r="C136" s="13"/>
-      <c r="D136" s="13"/>
-      <c r="E136" s="13"/>
-      <c r="F136" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G136" s="23" t="s">
+      <c r="A136" s="38" t="s">
         <v>230</v>
+      </c>
+      <c r="B136" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C136" s="29"/>
+      <c r="D136" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E136" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G136" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
@@ -4578,11 +4756,11 @@
       <c r="C137" s="13"/>
       <c r="D137" s="13"/>
       <c r="E137" s="13"/>
-      <c r="F137" s="66" t="s">
-        <v>218</v>
-      </c>
-      <c r="G137" s="67" t="s">
-        <v>200</v>
+      <c r="F137" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G137" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
@@ -4611,10 +4789,10 @@
       <c r="D138" s="13"/>
       <c r="E138" s="13"/>
       <c r="F138" s="14" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G138" s="23" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
@@ -4637,11 +4815,11 @@
       <c r="Z138" s="4"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="22"/>
-      <c r="B139" s="13"/>
-      <c r="C139" s="13"/>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
+      <c r="A139" s="24"/>
+      <c r="B139" s="16"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
       <c r="F139" s="14" t="s">
         <v>221</v>
       </c>
@@ -4669,16 +4847,24 @@
       <c r="Z139" s="4"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="22"/>
-      <c r="B140" s="13"/>
-      <c r="C140" s="13"/>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
-      <c r="F140" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="G140" s="23" t="s">
-        <v>232</v>
+      <c r="A140" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="B140" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="C140" s="29"/>
+      <c r="D140" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E140" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G140" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
@@ -4701,16 +4887,16 @@
       <c r="Z140" s="4"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="24"/>
-      <c r="B141" s="16"/>
-      <c r="C141" s="16"/>
-      <c r="D141" s="16"/>
-      <c r="E141" s="16"/>
+      <c r="A141" s="22"/>
+      <c r="B141" s="13"/>
+      <c r="C141" s="13"/>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
       <c r="F141" s="14" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G141" s="23" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
@@ -4732,25 +4918,17 @@
       <c r="Y141" s="4"/>
       <c r="Z141" s="4"/>
     </row>
-    <row r="142" ht="25.5" customHeight="1">
-      <c r="A142" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="B142" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="C142" s="29"/>
-      <c r="D142" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E142" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F142" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G142" s="42" t="s">
-        <v>215</v>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="22"/>
+      <c r="B142" s="13"/>
+      <c r="C142" s="13"/>
+      <c r="D142" s="13"/>
+      <c r="E142" s="13"/>
+      <c r="F142" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G142" s="23" t="s">
+        <v>237</v>
       </c>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
@@ -4773,16 +4951,16 @@
       <c r="Z142" s="4"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="24"/>
-      <c r="B143" s="16"/>
-      <c r="C143" s="16"/>
-      <c r="D143" s="16"/>
-      <c r="E143" s="16"/>
+      <c r="A143" s="22"/>
+      <c r="B143" s="13"/>
+      <c r="C143" s="13"/>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
       <c r="F143" s="14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G143" s="23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
@@ -4804,25 +4982,17 @@
       <c r="Y143" s="4"/>
       <c r="Z143" s="4"/>
     </row>
-    <row r="144" ht="25.5" customHeight="1">
-      <c r="A144" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="B144" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="C144" s="29"/>
-      <c r="D144" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E144" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F144" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G144" s="42" t="s">
-        <v>215</v>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="24"/>
+      <c r="B144" s="16"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="16"/>
+      <c r="E144" s="16"/>
+      <c r="F144" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G144" s="23" t="s">
+        <v>241</v>
       </c>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
@@ -4845,16 +5015,24 @@
       <c r="Z144" s="4"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="22"/>
-      <c r="B145" s="13"/>
-      <c r="C145" s="13"/>
-      <c r="D145" s="13"/>
-      <c r="E145" s="13"/>
-      <c r="F145" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="G145" s="23" t="s">
-        <v>174</v>
+      <c r="A145" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="B145" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C145" s="29"/>
+      <c r="D145" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G145" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
@@ -4883,10 +5061,10 @@
       <c r="D146" s="13"/>
       <c r="E146" s="13"/>
       <c r="F146" s="14" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G146" s="23" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
@@ -4909,16 +5087,16 @@
       <c r="Z146" s="4"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="24"/>
-      <c r="B147" s="16"/>
-      <c r="C147" s="16"/>
-      <c r="D147" s="16"/>
-      <c r="E147" s="16"/>
+      <c r="A147" s="22"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
       <c r="F147" s="14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G147" s="23" t="s">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
@@ -4941,24 +5119,16 @@
       <c r="Z147" s="4"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="B148" s="29" t="s">
+      <c r="A148" s="22"/>
+      <c r="B148" s="13"/>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="C148" s="29"/>
-      <c r="D148" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E148" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F148" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G148" s="42" t="s">
-        <v>215</v>
+      <c r="G148" s="23" t="s">
+        <v>246</v>
       </c>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
@@ -4981,16 +5151,16 @@
       <c r="Z148" s="4"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="22"/>
-      <c r="B149" s="13"/>
-      <c r="C149" s="13"/>
-      <c r="D149" s="13"/>
-      <c r="E149" s="13"/>
+      <c r="A149" s="24"/>
+      <c r="B149" s="16"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
       <c r="F149" s="14" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G149" s="23" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
@@ -5012,17 +5182,25 @@
       <c r="Y149" s="4"/>
       <c r="Z149" s="4"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="22"/>
-      <c r="B150" s="13"/>
-      <c r="C150" s="13"/>
-      <c r="D150" s="13"/>
-      <c r="E150" s="13"/>
-      <c r="F150" s="14" t="s">
+    <row r="150" ht="38.25" customHeight="1">
+      <c r="A150" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="B150" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="G150" s="23" t="s">
-        <v>249</v>
+      <c r="C150" s="29"/>
+      <c r="D150" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G150" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
@@ -5045,16 +5223,16 @@
       <c r="Z150" s="4"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="24"/>
-      <c r="B151" s="16"/>
-      <c r="C151" s="16"/>
-      <c r="D151" s="16"/>
-      <c r="E151" s="16"/>
+      <c r="A151" s="22"/>
+      <c r="B151" s="13"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="14" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="G151" s="23" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
@@ -5077,24 +5255,16 @@
       <c r="Z151" s="4"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="B152" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="C152" s="29"/>
-      <c r="D152" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E152" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F152" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G152" s="42" t="s">
-        <v>215</v>
+      <c r="A152" s="22"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
+      <c r="F152" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G152" s="23" t="s">
+        <v>250</v>
       </c>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -5123,10 +5293,10 @@
       <c r="D153" s="13"/>
       <c r="E153" s="13"/>
       <c r="F153" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G153" s="23" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
@@ -5149,16 +5319,16 @@
       <c r="Z153" s="4"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="22"/>
-      <c r="B154" s="13"/>
-      <c r="C154" s="13"/>
-      <c r="D154" s="13"/>
-      <c r="E154" s="13"/>
+      <c r="A154" s="24"/>
+      <c r="B154" s="16"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="16"/>
       <c r="F154" s="14" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="G154" s="23" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
@@ -5181,16 +5351,24 @@
       <c r="Z154" s="4"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="24"/>
-      <c r="B155" s="16"/>
-      <c r="C155" s="16"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="G155" s="23" t="s">
-        <v>243</v>
+      <c r="A155" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="B155" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="C155" s="29"/>
+      <c r="D155" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E155" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F155" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G155" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
@@ -5213,24 +5391,16 @@
       <c r="Z155" s="4"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="B156" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="C156" s="29"/>
-      <c r="D156" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E156" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F156" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G156" s="42" t="s">
-        <v>215</v>
+      <c r="A156" s="22"/>
+      <c r="B156" s="13"/>
+      <c r="C156" s="13"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="13"/>
+      <c r="F156" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G156" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
@@ -5259,10 +5429,10 @@
       <c r="D157" s="13"/>
       <c r="E157" s="13"/>
       <c r="F157" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
@@ -5291,10 +5461,10 @@
       <c r="D158" s="13"/>
       <c r="E158" s="13"/>
       <c r="F158" s="14" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
@@ -5317,16 +5487,16 @@
       <c r="Z158" s="4"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="22"/>
-      <c r="B159" s="13"/>
-      <c r="C159" s="13"/>
-      <c r="D159" s="13"/>
-      <c r="E159" s="13"/>
+      <c r="A159" s="24"/>
+      <c r="B159" s="16"/>
+      <c r="C159" s="16"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="16"/>
       <c r="F159" s="14" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="G159" s="23" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
@@ -5348,17 +5518,25 @@
       <c r="Y159" s="4"/>
       <c r="Z159" s="4"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="24"/>
-      <c r="B160" s="16"/>
-      <c r="C160" s="16"/>
-      <c r="D160" s="16"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G160" s="23" t="s">
-        <v>262</v>
+    <row r="160" ht="38.25" customHeight="1">
+      <c r="A160" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="B160" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="C160" s="29"/>
+      <c r="D160" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E160" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G160" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
@@ -5381,24 +5559,16 @@
       <c r="Z160" s="4"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="B161" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="C161" s="29"/>
-      <c r="D161" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E161" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F161" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G161" s="42" t="s">
-        <v>215</v>
+      <c r="A161" s="22"/>
+      <c r="B161" s="13"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="13"/>
+      <c r="F161" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G161" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
@@ -5421,16 +5591,16 @@
       <c r="Z161" s="4"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="22"/>
-      <c r="B162" s="13"/>
-      <c r="C162" s="13"/>
-      <c r="D162" s="13"/>
-      <c r="E162" s="13"/>
-      <c r="F162" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="G162" s="23" t="s">
-        <v>254</v>
+      <c r="A162" s="31"/>
+      <c r="B162" s="32"/>
+      <c r="C162" s="32"/>
+      <c r="D162" s="32"/>
+      <c r="E162" s="32"/>
+      <c r="F162" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="G162" s="34" t="s">
+        <v>260</v>
       </c>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
@@ -5453,17 +5623,15 @@
       <c r="Z162" s="4"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="22"/>
-      <c r="B163" s="13"/>
-      <c r="C163" s="13"/>
-      <c r="D163" s="13"/>
-      <c r="E163" s="13"/>
-      <c r="F163" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="G163" s="23" t="s">
-        <v>200</v>
-      </c>
+      <c r="A163" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="8"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
@@ -5485,16 +5653,24 @@
       <c r="Z163" s="4"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="22"/>
-      <c r="B164" s="13"/>
-      <c r="C164" s="13"/>
-      <c r="D164" s="13"/>
-      <c r="E164" s="13"/>
-      <c r="F164" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="G164" s="23" t="s">
-        <v>267</v>
+      <c r="A164" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="B164" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="C164" s="47"/>
+      <c r="D164" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="F164" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="G164" s="21" t="s">
+        <v>265</v>
       </c>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
@@ -5516,17 +5692,25 @@
       <c r="Y164" s="4"/>
       <c r="Z164" s="4"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="24"/>
-      <c r="B165" s="16"/>
-      <c r="C165" s="16"/>
-      <c r="D165" s="16"/>
-      <c r="E165" s="16"/>
+    <row r="165" ht="63.75" customHeight="1">
+      <c r="A165" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="B165" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="C165" s="29"/>
+      <c r="D165" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165" s="29" t="s">
+        <v>192</v>
+      </c>
       <c r="F165" s="14" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="G165" s="23" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
@@ -5548,25 +5732,17 @@
       <c r="Y165" s="4"/>
       <c r="Z165" s="4"/>
     </row>
-    <row r="166" ht="38.25" customHeight="1">
-      <c r="A166" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="B166" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="C166" s="29"/>
-      <c r="D166" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E166" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F166" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G166" s="42" t="s">
-        <v>215</v>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="22"/>
+      <c r="B166" s="13"/>
+      <c r="C166" s="13"/>
+      <c r="D166" s="13"/>
+      <c r="E166" s="13"/>
+      <c r="F166" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="G166" s="23" t="s">
+        <v>271</v>
       </c>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
@@ -5589,16 +5765,16 @@
       <c r="Z166" s="4"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="22"/>
-      <c r="B167" s="13"/>
-      <c r="C167" s="13"/>
-      <c r="D167" s="13"/>
-      <c r="E167" s="13"/>
+      <c r="A167" s="24"/>
+      <c r="B167" s="16"/>
+      <c r="C167" s="16"/>
+      <c r="D167" s="16"/>
+      <c r="E167" s="16"/>
       <c r="F167" s="14" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="G167" s="23" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
@@ -5620,17 +5796,25 @@
       <c r="Y167" s="4"/>
       <c r="Z167" s="4"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="22"/>
-      <c r="B168" s="13"/>
-      <c r="C168" s="13"/>
-      <c r="D168" s="13"/>
-      <c r="E168" s="13"/>
+    <row r="168" ht="63.75" customHeight="1">
+      <c r="A168" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="B168" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="C168" s="29"/>
+      <c r="D168" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" s="29" t="s">
+        <v>192</v>
+      </c>
       <c r="F168" s="14" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G168" s="23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
@@ -5659,10 +5843,10 @@
       <c r="D169" s="13"/>
       <c r="E169" s="13"/>
       <c r="F169" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G169" s="23" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
@@ -5685,16 +5869,16 @@
       <c r="Z169" s="4"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="24"/>
-      <c r="B170" s="16"/>
-      <c r="C170" s="16"/>
-      <c r="D170" s="16"/>
-      <c r="E170" s="16"/>
-      <c r="F170" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G170" s="23" t="s">
-        <v>273</v>
+      <c r="A170" s="31"/>
+      <c r="B170" s="32"/>
+      <c r="C170" s="32"/>
+      <c r="D170" s="32"/>
+      <c r="E170" s="32"/>
+      <c r="F170" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="G170" s="34" t="s">
+        <v>279</v>
       </c>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
@@ -5717,25 +5901,15 @@
       <c r="Z170" s="4"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="B171" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="C171" s="29"/>
-      <c r="D171" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E171" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F171" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G171" s="42" t="s">
-        <v>215</v>
-      </c>
+      <c r="A171" s="68" t="s">
+        <v>280</v>
+      </c>
+      <c r="B171" s="44"/>
+      <c r="C171" s="44"/>
+      <c r="D171" s="44"/>
+      <c r="E171" s="44"/>
+      <c r="F171" s="44"/>
+      <c r="G171" s="69"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
@@ -5757,16 +5931,24 @@
       <c r="Z171" s="4"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="22"/>
-      <c r="B172" s="13"/>
-      <c r="C172" s="13"/>
-      <c r="D172" s="13"/>
-      <c r="E172" s="13"/>
-      <c r="F172" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="G172" s="23" t="s">
-        <v>254</v>
+      <c r="A172" s="55" t="s">
+        <v>281</v>
+      </c>
+      <c r="B172" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="C172" s="37"/>
+      <c r="D172" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E172" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F172" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="G172" s="21" t="s">
+        <v>284</v>
       </c>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
@@ -5795,10 +5977,10 @@
       <c r="D173" s="13"/>
       <c r="E173" s="13"/>
       <c r="F173" s="14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="G173" s="23" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
@@ -5821,16 +6003,16 @@
       <c r="Z173" s="4"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="22"/>
-      <c r="B174" s="13"/>
-      <c r="C174" s="13"/>
-      <c r="D174" s="13"/>
-      <c r="E174" s="13"/>
+      <c r="A174" s="24"/>
+      <c r="B174" s="16"/>
+      <c r="C174" s="16"/>
+      <c r="D174" s="16"/>
+      <c r="E174" s="16"/>
       <c r="F174" s="14" t="s">
-        <v>272</v>
+        <v>148</v>
       </c>
       <c r="G174" s="23" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
@@ -5853,16 +6035,24 @@
       <c r="Z174" s="4"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="24"/>
-      <c r="B175" s="16"/>
-      <c r="C175" s="16"/>
-      <c r="D175" s="16"/>
-      <c r="E175" s="16"/>
-      <c r="F175" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G175" s="23" t="s">
-        <v>273</v>
+      <c r="A175" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="B175" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="C175" s="29"/>
+      <c r="D175" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E175" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G175" s="67" t="s">
+        <v>284</v>
       </c>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
@@ -5884,25 +6074,17 @@
       <c r="Y175" s="4"/>
       <c r="Z175" s="4"/>
     </row>
-    <row r="176" ht="38.25" customHeight="1">
-      <c r="A176" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="B176" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="C176" s="29"/>
-      <c r="D176" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E176" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F176" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G176" s="42" t="s">
-        <v>215</v>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="22"/>
+      <c r="B176" s="13"/>
+      <c r="C176" s="13"/>
+      <c r="D176" s="13"/>
+      <c r="E176" s="13"/>
+      <c r="F176" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="G176" s="23" t="s">
+        <v>290</v>
       </c>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
@@ -5925,16 +6107,16 @@
       <c r="Z176" s="4"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="22"/>
-      <c r="B177" s="13"/>
-      <c r="C177" s="13"/>
-      <c r="D177" s="13"/>
-      <c r="E177" s="13"/>
+      <c r="A177" s="24"/>
+      <c r="B177" s="16"/>
+      <c r="C177" s="16"/>
+      <c r="D177" s="16"/>
+      <c r="E177" s="16"/>
       <c r="F177" s="14" t="s">
-        <v>253</v>
+        <v>148</v>
       </c>
       <c r="G177" s="23" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
@@ -5957,16 +6139,24 @@
       <c r="Z177" s="4"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="31"/>
-      <c r="B178" s="32"/>
-      <c r="C178" s="32"/>
-      <c r="D178" s="32"/>
-      <c r="E178" s="32"/>
-      <c r="F178" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="G178" s="34" t="s">
-        <v>281</v>
+      <c r="A178" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="B178" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="C178" s="29"/>
+      <c r="D178" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E178" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G178" s="67" t="s">
+        <v>284</v>
       </c>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
@@ -5989,15 +6179,17 @@
       <c r="Z178" s="4"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="35" t="s">
-        <v>282</v>
-      </c>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-      <c r="G179" s="8"/>
+      <c r="A179" s="22"/>
+      <c r="B179" s="13"/>
+      <c r="C179" s="13"/>
+      <c r="D179" s="13"/>
+      <c r="E179" s="13"/>
+      <c r="F179" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="G179" s="23" t="s">
+        <v>290</v>
+      </c>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -6019,24 +6211,16 @@
       <c r="Z179" s="4"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="48" t="s">
-        <v>283</v>
-      </c>
-      <c r="B180" s="49" t="s">
-        <v>284</v>
-      </c>
-      <c r="C180" s="49"/>
-      <c r="D180" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E180" s="49" t="s">
-        <v>213</v>
-      </c>
-      <c r="F180" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="G180" s="21" t="s">
-        <v>286</v>
+      <c r="A180" s="24"/>
+      <c r="B180" s="16"/>
+      <c r="C180" s="16"/>
+      <c r="D180" s="16"/>
+      <c r="E180" s="16"/>
+      <c r="F180" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G180" s="23" t="s">
+        <v>295</v>
       </c>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
@@ -6058,25 +6242,25 @@
       <c r="Y180" s="4"/>
       <c r="Z180" s="4"/>
     </row>
-    <row r="181" ht="63.75" customHeight="1">
-      <c r="A181" s="28" t="s">
-        <v>287</v>
+    <row r="181" ht="33.0" customHeight="1">
+      <c r="A181" s="38" t="s">
+        <v>296</v>
       </c>
       <c r="B181" s="29" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C181" s="29"/>
       <c r="D181" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E181" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F181" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="G181" s="23" t="s">
-        <v>290</v>
+        <v>192</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G181" s="67" t="s">
+        <v>284</v>
       </c>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
@@ -6098,17 +6282,17 @@
       <c r="Y181" s="4"/>
       <c r="Z181" s="4"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="22"/>
-      <c r="B182" s="13"/>
-      <c r="C182" s="13"/>
-      <c r="D182" s="13"/>
-      <c r="E182" s="13"/>
-      <c r="F182" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="G182" s="23" t="s">
-        <v>292</v>
+    <row r="182" ht="33.0" customHeight="1">
+      <c r="A182" s="31"/>
+      <c r="B182" s="32"/>
+      <c r="C182" s="32"/>
+      <c r="D182" s="32"/>
+      <c r="E182" s="32"/>
+      <c r="F182" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="G182" s="34" t="s">
+        <v>298</v>
       </c>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
@@ -6131,554 +6315,148 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="24"/>
-      <c r="B183" s="16"/>
-      <c r="C183" s="16"/>
-      <c r="D183" s="16"/>
-      <c r="E183" s="16"/>
-      <c r="F183" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="G183" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="H183" s="4"/>
-      <c r="I183" s="4"/>
-      <c r="J183" s="4"/>
-      <c r="K183" s="4"/>
-      <c r="L183" s="4"/>
-      <c r="M183" s="4"/>
-      <c r="N183" s="4"/>
-      <c r="O183" s="4"/>
-      <c r="P183" s="4"/>
-      <c r="Q183" s="4"/>
-      <c r="R183" s="4"/>
-      <c r="S183" s="4"/>
-      <c r="T183" s="4"/>
-      <c r="U183" s="4"/>
-      <c r="V183" s="4"/>
-      <c r="W183" s="4"/>
-      <c r="X183" s="4"/>
-      <c r="Y183" s="4"/>
-      <c r="Z183" s="4"/>
-    </row>
-    <row r="184" ht="63.75" customHeight="1">
-      <c r="A184" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="B184" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="C184" s="29"/>
-      <c r="D184" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E184" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F184" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="G184" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="H184" s="4"/>
-      <c r="I184" s="4"/>
-      <c r="J184" s="4"/>
-      <c r="K184" s="4"/>
-      <c r="L184" s="4"/>
-      <c r="M184" s="4"/>
-      <c r="N184" s="4"/>
-      <c r="O184" s="4"/>
-      <c r="P184" s="4"/>
-      <c r="Q184" s="4"/>
-      <c r="R184" s="4"/>
-      <c r="S184" s="4"/>
-      <c r="T184" s="4"/>
-      <c r="U184" s="4"/>
-      <c r="V184" s="4"/>
-      <c r="W184" s="4"/>
-      <c r="X184" s="4"/>
-      <c r="Y184" s="4"/>
-      <c r="Z184" s="4"/>
+      <c r="A183" s="1"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="1"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="22"/>
-      <c r="B185" s="13"/>
-      <c r="C185" s="13"/>
-      <c r="D185" s="13"/>
-      <c r="E185" s="13"/>
-      <c r="F185" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G185" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="H185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
-      <c r="K185" s="4"/>
-      <c r="L185" s="4"/>
-      <c r="M185" s="4"/>
-      <c r="N185" s="4"/>
-      <c r="O185" s="4"/>
-      <c r="P185" s="4"/>
-      <c r="Q185" s="4"/>
-      <c r="R185" s="4"/>
-      <c r="S185" s="4"/>
-      <c r="T185" s="4"/>
-      <c r="U185" s="4"/>
-      <c r="V185" s="4"/>
-      <c r="W185" s="4"/>
-      <c r="X185" s="4"/>
-      <c r="Y185" s="4"/>
-      <c r="Z185" s="4"/>
+      <c r="A185" s="1"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="31"/>
-      <c r="B186" s="32"/>
-      <c r="C186" s="32"/>
-      <c r="D186" s="32"/>
-      <c r="E186" s="32"/>
-      <c r="F186" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="G186" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="H186" s="4"/>
-      <c r="I186" s="4"/>
-      <c r="J186" s="4"/>
-      <c r="K186" s="4"/>
-      <c r="L186" s="4"/>
-      <c r="M186" s="4"/>
-      <c r="N186" s="4"/>
-      <c r="O186" s="4"/>
-      <c r="P186" s="4"/>
-      <c r="Q186" s="4"/>
-      <c r="R186" s="4"/>
-      <c r="S186" s="4"/>
-      <c r="T186" s="4"/>
-      <c r="U186" s="4"/>
-      <c r="V186" s="4"/>
-      <c r="W186" s="4"/>
-      <c r="X186" s="4"/>
-      <c r="Y186" s="4"/>
-      <c r="Z186" s="4"/>
+      <c r="A186" s="1"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="B187" s="46"/>
-      <c r="C187" s="46"/>
-      <c r="D187" s="46"/>
-      <c r="E187" s="46"/>
-      <c r="F187" s="46"/>
-      <c r="G187" s="69"/>
-      <c r="H187" s="4"/>
-      <c r="I187" s="4"/>
-      <c r="J187" s="4"/>
-      <c r="K187" s="4"/>
-      <c r="L187" s="4"/>
-      <c r="M187" s="4"/>
-      <c r="N187" s="4"/>
-      <c r="O187" s="4"/>
-      <c r="P187" s="4"/>
-      <c r="Q187" s="4"/>
-      <c r="R187" s="4"/>
-      <c r="S187" s="4"/>
-      <c r="T187" s="4"/>
-      <c r="U187" s="4"/>
-      <c r="V187" s="4"/>
-      <c r="W187" s="4"/>
-      <c r="X187" s="4"/>
-      <c r="Y187" s="4"/>
-      <c r="Z187" s="4"/>
+      <c r="A187" s="1"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="B188" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="C188" s="37"/>
-      <c r="D188" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E188" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="F188" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="G188" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="H188" s="4"/>
-      <c r="I188" s="4"/>
-      <c r="J188" s="4"/>
-      <c r="K188" s="4"/>
-      <c r="L188" s="4"/>
-      <c r="M188" s="4"/>
-      <c r="N188" s="4"/>
-      <c r="O188" s="4"/>
-      <c r="P188" s="4"/>
-      <c r="Q188" s="4"/>
-      <c r="R188" s="4"/>
-      <c r="S188" s="4"/>
-      <c r="T188" s="4"/>
-      <c r="U188" s="4"/>
-      <c r="V188" s="4"/>
-      <c r="W188" s="4"/>
-      <c r="X188" s="4"/>
-      <c r="Y188" s="4"/>
-      <c r="Z188" s="4"/>
+      <c r="A188" s="1"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="22"/>
-      <c r="B189" s="13"/>
-      <c r="C189" s="13"/>
-      <c r="D189" s="13"/>
-      <c r="E189" s="13"/>
-      <c r="F189" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="G189" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="H189" s="4"/>
-      <c r="I189" s="4"/>
-      <c r="J189" s="4"/>
-      <c r="K189" s="4"/>
-      <c r="L189" s="4"/>
-      <c r="M189" s="4"/>
-      <c r="N189" s="4"/>
-      <c r="O189" s="4"/>
-      <c r="P189" s="4"/>
-      <c r="Q189" s="4"/>
-      <c r="R189" s="4"/>
-      <c r="S189" s="4"/>
-      <c r="T189" s="4"/>
-      <c r="U189" s="4"/>
-      <c r="V189" s="4"/>
-      <c r="W189" s="4"/>
-      <c r="X189" s="4"/>
-      <c r="Y189" s="4"/>
-      <c r="Z189" s="4"/>
+      <c r="A189" s="1"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="24"/>
-      <c r="B190" s="16"/>
-      <c r="C190" s="16"/>
-      <c r="D190" s="16"/>
-      <c r="E190" s="16"/>
-      <c r="F190" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G190" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="H190" s="4"/>
-      <c r="I190" s="4"/>
-      <c r="J190" s="4"/>
-      <c r="K190" s="4"/>
-      <c r="L190" s="4"/>
-      <c r="M190" s="4"/>
-      <c r="N190" s="4"/>
-      <c r="O190" s="4"/>
-      <c r="P190" s="4"/>
-      <c r="Q190" s="4"/>
-      <c r="R190" s="4"/>
-      <c r="S190" s="4"/>
-      <c r="T190" s="4"/>
-      <c r="U190" s="4"/>
-      <c r="V190" s="4"/>
-      <c r="W190" s="4"/>
-      <c r="X190" s="4"/>
-      <c r="Y190" s="4"/>
-      <c r="Z190" s="4"/>
+      <c r="A190" s="1"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="B191" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="C191" s="29"/>
-      <c r="D191" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E191" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G191" s="42" t="s">
-        <v>305</v>
-      </c>
-      <c r="H191" s="4"/>
-      <c r="I191" s="4"/>
-      <c r="J191" s="4"/>
-      <c r="K191" s="4"/>
-      <c r="L191" s="4"/>
-      <c r="M191" s="4"/>
-      <c r="N191" s="4"/>
-      <c r="O191" s="4"/>
-      <c r="P191" s="4"/>
-      <c r="Q191" s="4"/>
-      <c r="R191" s="4"/>
-      <c r="S191" s="4"/>
-      <c r="T191" s="4"/>
-      <c r="U191" s="4"/>
-      <c r="V191" s="4"/>
-      <c r="W191" s="4"/>
-      <c r="X191" s="4"/>
-      <c r="Y191" s="4"/>
-      <c r="Z191" s="4"/>
+      <c r="A191" s="1"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="22"/>
-      <c r="B192" s="13"/>
-      <c r="C192" s="13"/>
-      <c r="D192" s="13"/>
-      <c r="E192" s="13"/>
-      <c r="F192" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="G192" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="H192" s="4"/>
-      <c r="I192" s="4"/>
-      <c r="J192" s="4"/>
-      <c r="K192" s="4"/>
-      <c r="L192" s="4"/>
-      <c r="M192" s="4"/>
-      <c r="N192" s="4"/>
-      <c r="O192" s="4"/>
-      <c r="P192" s="4"/>
-      <c r="Q192" s="4"/>
-      <c r="R192" s="4"/>
-      <c r="S192" s="4"/>
-      <c r="T192" s="4"/>
-      <c r="U192" s="4"/>
-      <c r="V192" s="4"/>
-      <c r="W192" s="4"/>
-      <c r="X192" s="4"/>
-      <c r="Y192" s="4"/>
-      <c r="Z192" s="4"/>
+      <c r="A192" s="1"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="24"/>
-      <c r="B193" s="16"/>
-      <c r="C193" s="16"/>
-      <c r="D193" s="16"/>
-      <c r="E193" s="16"/>
-      <c r="F193" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G193" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="H193" s="4"/>
-      <c r="I193" s="4"/>
-      <c r="J193" s="4"/>
-      <c r="K193" s="4"/>
-      <c r="L193" s="4"/>
-      <c r="M193" s="4"/>
-      <c r="N193" s="4"/>
-      <c r="O193" s="4"/>
-      <c r="P193" s="4"/>
-      <c r="Q193" s="4"/>
-      <c r="R193" s="4"/>
-      <c r="S193" s="4"/>
-      <c r="T193" s="4"/>
-      <c r="U193" s="4"/>
-      <c r="V193" s="4"/>
-      <c r="W193" s="4"/>
-      <c r="X193" s="4"/>
-      <c r="Y193" s="4"/>
-      <c r="Z193" s="4"/>
+      <c r="A193" s="1"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="B194" s="29" t="s">
-        <v>314</v>
-      </c>
-      <c r="C194" s="29"/>
-      <c r="D194" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E194" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F194" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G194" s="42" t="s">
-        <v>305</v>
-      </c>
-      <c r="H194" s="4"/>
-      <c r="I194" s="4"/>
-      <c r="J194" s="4"/>
-      <c r="K194" s="4"/>
-      <c r="L194" s="4"/>
-      <c r="M194" s="4"/>
-      <c r="N194" s="4"/>
-      <c r="O194" s="4"/>
-      <c r="P194" s="4"/>
-      <c r="Q194" s="4"/>
-      <c r="R194" s="4"/>
-      <c r="S194" s="4"/>
-      <c r="T194" s="4"/>
-      <c r="U194" s="4"/>
-      <c r="V194" s="4"/>
-      <c r="W194" s="4"/>
-      <c r="X194" s="4"/>
-      <c r="Y194" s="4"/>
-      <c r="Z194" s="4"/>
+      <c r="A194" s="1"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="22"/>
-      <c r="B195" s="13"/>
-      <c r="C195" s="13"/>
-      <c r="D195" s="13"/>
-      <c r="E195" s="13"/>
-      <c r="F195" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="G195" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="H195" s="4"/>
-      <c r="I195" s="4"/>
-      <c r="J195" s="4"/>
-      <c r="K195" s="4"/>
-      <c r="L195" s="4"/>
-      <c r="M195" s="4"/>
-      <c r="N195" s="4"/>
-      <c r="O195" s="4"/>
-      <c r="P195" s="4"/>
-      <c r="Q195" s="4"/>
-      <c r="R195" s="4"/>
-      <c r="S195" s="4"/>
-      <c r="T195" s="4"/>
-      <c r="U195" s="4"/>
-      <c r="V195" s="4"/>
-      <c r="W195" s="4"/>
-      <c r="X195" s="4"/>
-      <c r="Y195" s="4"/>
-      <c r="Z195" s="4"/>
+      <c r="A195" s="1"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="24"/>
-      <c r="B196" s="16"/>
-      <c r="C196" s="16"/>
-      <c r="D196" s="16"/>
-      <c r="E196" s="16"/>
-      <c r="F196" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G196" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="H196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
-      <c r="K196" s="4"/>
-      <c r="L196" s="4"/>
-      <c r="M196" s="4"/>
-      <c r="N196" s="4"/>
-      <c r="O196" s="4"/>
-      <c r="P196" s="4"/>
-      <c r="Q196" s="4"/>
-      <c r="R196" s="4"/>
-      <c r="S196" s="4"/>
-      <c r="T196" s="4"/>
-      <c r="U196" s="4"/>
-      <c r="V196" s="4"/>
-      <c r="W196" s="4"/>
-      <c r="X196" s="4"/>
-      <c r="Y196" s="4"/>
-      <c r="Z196" s="4"/>
-    </row>
-    <row r="197" ht="33.0" customHeight="1">
-      <c r="A197" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="B197" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="C197" s="29"/>
-      <c r="D197" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E197" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G197" s="42" t="s">
-        <v>305</v>
-      </c>
-      <c r="H197" s="4"/>
-      <c r="I197" s="4"/>
-      <c r="J197" s="4"/>
-      <c r="K197" s="4"/>
-      <c r="L197" s="4"/>
-      <c r="M197" s="4"/>
-      <c r="N197" s="4"/>
-      <c r="O197" s="4"/>
-      <c r="P197" s="4"/>
-      <c r="Q197" s="4"/>
-      <c r="R197" s="4"/>
-      <c r="S197" s="4"/>
-      <c r="T197" s="4"/>
-      <c r="U197" s="4"/>
-      <c r="V197" s="4"/>
-      <c r="W197" s="4"/>
-      <c r="X197" s="4"/>
-      <c r="Y197" s="4"/>
-      <c r="Z197" s="4"/>
-    </row>
-    <row r="198" ht="33.0" customHeight="1">
-      <c r="A198" s="31"/>
-      <c r="B198" s="32"/>
-      <c r="C198" s="32"/>
-      <c r="D198" s="32"/>
-      <c r="E198" s="32"/>
-      <c r="F198" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="G198" s="34" t="s">
-        <v>319</v>
-      </c>
-      <c r="H198" s="4"/>
-      <c r="I198" s="4"/>
-      <c r="J198" s="4"/>
-      <c r="K198" s="4"/>
-      <c r="L198" s="4"/>
-      <c r="M198" s="4"/>
-      <c r="N198" s="4"/>
-      <c r="O198" s="4"/>
-      <c r="P198" s="4"/>
-      <c r="Q198" s="4"/>
-      <c r="R198" s="4"/>
-      <c r="S198" s="4"/>
-      <c r="T198" s="4"/>
-      <c r="U198" s="4"/>
-      <c r="V198" s="4"/>
-      <c r="W198" s="4"/>
-      <c r="X198" s="4"/>
-      <c r="Y198" s="4"/>
-      <c r="Z198" s="4"/>
+      <c r="A196" s="1"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="1"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="1"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1"/>
@@ -13754,271 +13532,127 @@
       <c r="F984" s="2"/>
       <c r="G984" s="2"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="1"/>
-      <c r="B985" s="2"/>
-      <c r="C985" s="2"/>
-      <c r="D985" s="1"/>
-      <c r="E985" s="1"/>
-      <c r="F985" s="2"/>
-      <c r="G985" s="2"/>
-    </row>
-    <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="1"/>
-      <c r="B986" s="2"/>
-      <c r="C986" s="2"/>
-      <c r="D986" s="1"/>
-      <c r="E986" s="1"/>
-      <c r="F986" s="2"/>
-      <c r="G986" s="2"/>
-    </row>
-    <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="1"/>
-      <c r="B987" s="2"/>
-      <c r="C987" s="2"/>
-      <c r="D987" s="1"/>
-      <c r="E987" s="1"/>
-      <c r="F987" s="2"/>
-      <c r="G987" s="2"/>
-    </row>
-    <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="1"/>
-      <c r="B988" s="2"/>
-      <c r="C988" s="2"/>
-      <c r="D988" s="1"/>
-      <c r="E988" s="1"/>
-      <c r="F988" s="2"/>
-      <c r="G988" s="2"/>
-    </row>
-    <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="1"/>
-      <c r="B989" s="2"/>
-      <c r="C989" s="2"/>
-      <c r="D989" s="1"/>
-      <c r="E989" s="1"/>
-      <c r="F989" s="2"/>
-      <c r="G989" s="2"/>
-    </row>
-    <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="1"/>
-      <c r="B990" s="2"/>
-      <c r="C990" s="2"/>
-      <c r="D990" s="1"/>
-      <c r="E990" s="1"/>
-      <c r="F990" s="2"/>
-      <c r="G990" s="2"/>
-    </row>
-    <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="1"/>
-      <c r="B991" s="2"/>
-      <c r="C991" s="2"/>
-      <c r="D991" s="1"/>
-      <c r="E991" s="1"/>
-      <c r="F991" s="2"/>
-      <c r="G991" s="2"/>
-    </row>
-    <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="1"/>
-      <c r="B992" s="2"/>
-      <c r="C992" s="2"/>
-      <c r="D992" s="1"/>
-      <c r="E992" s="1"/>
-      <c r="F992" s="2"/>
-      <c r="G992" s="2"/>
-    </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="1"/>
-      <c r="B993" s="2"/>
-      <c r="C993" s="2"/>
-      <c r="D993" s="1"/>
-      <c r="E993" s="1"/>
-      <c r="F993" s="2"/>
-      <c r="G993" s="2"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="1"/>
-      <c r="B994" s="2"/>
-      <c r="C994" s="2"/>
-      <c r="D994" s="1"/>
-      <c r="E994" s="1"/>
-      <c r="F994" s="2"/>
-      <c r="G994" s="2"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="1"/>
-      <c r="B995" s="2"/>
-      <c r="C995" s="2"/>
-      <c r="D995" s="1"/>
-      <c r="E995" s="1"/>
-      <c r="F995" s="2"/>
-      <c r="G995" s="2"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="1"/>
-      <c r="B996" s="2"/>
-      <c r="C996" s="2"/>
-      <c r="D996" s="1"/>
-      <c r="E996" s="1"/>
-      <c r="F996" s="2"/>
-      <c r="G996" s="2"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="1"/>
-      <c r="B997" s="2"/>
-      <c r="C997" s="2"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-      <c r="F997" s="2"/>
-      <c r="G997" s="2"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="1"/>
-      <c r="B998" s="2"/>
-      <c r="C998" s="2"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-      <c r="F998" s="2"/>
-      <c r="G998" s="2"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="1"/>
-      <c r="B999" s="2"/>
-      <c r="C999" s="2"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-      <c r="F999" s="2"/>
-      <c r="G999" s="2"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="1"/>
-      <c r="B1000" s="2"/>
-      <c r="C1000" s="2"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="2"/>
-      <c r="G1000" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="291">
-    <mergeCell ref="D135:D141"/>
-    <mergeCell ref="E135:E141"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A128:A134"/>
-    <mergeCell ref="B128:B134"/>
-    <mergeCell ref="C128:C134"/>
-    <mergeCell ref="D128:D134"/>
-    <mergeCell ref="E128:E134"/>
-    <mergeCell ref="A135:A141"/>
-    <mergeCell ref="C95:C97"/>
-    <mergeCell ref="D95:D97"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="E92:E94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="E95:E97"/>
-    <mergeCell ref="D101:D103"/>
-    <mergeCell ref="E101:E103"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="E104:E106"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="E107:E109"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="C98:C100"/>
-    <mergeCell ref="D98:D100"/>
-    <mergeCell ref="E98:E100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="D113:D115"/>
-    <mergeCell ref="E113:E115"/>
-    <mergeCell ref="B135:B141"/>
-    <mergeCell ref="C135:C141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="A166:A170"/>
-    <mergeCell ref="A171:A175"/>
-    <mergeCell ref="B171:B175"/>
-    <mergeCell ref="C171:C175"/>
-    <mergeCell ref="D171:D175"/>
-    <mergeCell ref="E171:E175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="B176:B178"/>
-    <mergeCell ref="C176:C178"/>
-    <mergeCell ref="A181:A183"/>
-    <mergeCell ref="B181:B183"/>
-    <mergeCell ref="C181:C183"/>
-    <mergeCell ref="D181:D183"/>
-    <mergeCell ref="E181:E183"/>
-    <mergeCell ref="D188:D190"/>
-    <mergeCell ref="E188:E190"/>
-    <mergeCell ref="A184:A186"/>
-    <mergeCell ref="B184:B186"/>
-    <mergeCell ref="C184:C186"/>
-    <mergeCell ref="D184:D186"/>
-    <mergeCell ref="E184:E186"/>
-    <mergeCell ref="A187:G187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="C197:C198"/>
-    <mergeCell ref="D197:D198"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="B194:B196"/>
-    <mergeCell ref="C194:C196"/>
-    <mergeCell ref="D194:D196"/>
-    <mergeCell ref="E194:E196"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="B197:B198"/>
-    <mergeCell ref="E197:E198"/>
-    <mergeCell ref="C148:C151"/>
-    <mergeCell ref="D148:D151"/>
-    <mergeCell ref="A144:A147"/>
-    <mergeCell ref="B144:B147"/>
-    <mergeCell ref="C144:C147"/>
-    <mergeCell ref="D144:D147"/>
-    <mergeCell ref="E144:E147"/>
-    <mergeCell ref="B148:B151"/>
-    <mergeCell ref="E148:E151"/>
-    <mergeCell ref="D156:D160"/>
-    <mergeCell ref="E156:E160"/>
-    <mergeCell ref="D161:D165"/>
-    <mergeCell ref="E161:E165"/>
-    <mergeCell ref="D166:D170"/>
-    <mergeCell ref="E166:E170"/>
-    <mergeCell ref="A148:A151"/>
-    <mergeCell ref="A152:A155"/>
-    <mergeCell ref="B152:B155"/>
-    <mergeCell ref="C152:C155"/>
-    <mergeCell ref="D152:D155"/>
-    <mergeCell ref="E152:E155"/>
-    <mergeCell ref="A156:A160"/>
-    <mergeCell ref="B156:B160"/>
-    <mergeCell ref="C156:C160"/>
-    <mergeCell ref="A161:A165"/>
-    <mergeCell ref="B161:B165"/>
-    <mergeCell ref="C161:C165"/>
-    <mergeCell ref="B166:B170"/>
-    <mergeCell ref="C166:C170"/>
-    <mergeCell ref="D176:D178"/>
-    <mergeCell ref="E176:E178"/>
-    <mergeCell ref="A179:G179"/>
-    <mergeCell ref="B188:B190"/>
-    <mergeCell ref="C188:C190"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="B191:B193"/>
-    <mergeCell ref="C191:C193"/>
-    <mergeCell ref="D191:D193"/>
-    <mergeCell ref="E191:E193"/>
+  <mergeCells count="260">
+    <mergeCell ref="D119:D125"/>
+    <mergeCell ref="E119:E125"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A112:A118"/>
+    <mergeCell ref="B112:B118"/>
+    <mergeCell ref="C112:C118"/>
+    <mergeCell ref="D112:D118"/>
+    <mergeCell ref="E112:E118"/>
+    <mergeCell ref="A119:A125"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="D79:D81"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="E79:E81"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="E85:E87"/>
+    <mergeCell ref="D88:D90"/>
+    <mergeCell ref="E88:E90"/>
+    <mergeCell ref="D91:D93"/>
+    <mergeCell ref="E91:E93"/>
+    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="D82:D84"/>
+    <mergeCell ref="E82:E84"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="A88:A90"/>
+    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="C91:C93"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="E97:E99"/>
+    <mergeCell ref="B119:B125"/>
+    <mergeCell ref="C119:C125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="E126:E127"/>
+    <mergeCell ref="A150:A154"/>
+    <mergeCell ref="A155:A159"/>
+    <mergeCell ref="B155:B159"/>
+    <mergeCell ref="C155:C159"/>
+    <mergeCell ref="D155:D159"/>
+    <mergeCell ref="E155:E159"/>
+    <mergeCell ref="A160:A162"/>
+    <mergeCell ref="B160:B162"/>
+    <mergeCell ref="C160:C162"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="B165:B167"/>
+    <mergeCell ref="C165:C167"/>
+    <mergeCell ref="D165:D167"/>
+    <mergeCell ref="E165:E167"/>
+    <mergeCell ref="D172:D174"/>
+    <mergeCell ref="E172:E174"/>
+    <mergeCell ref="A168:A170"/>
+    <mergeCell ref="B168:B170"/>
+    <mergeCell ref="C168:C170"/>
+    <mergeCell ref="D168:D170"/>
+    <mergeCell ref="E168:E170"/>
+    <mergeCell ref="A171:G171"/>
+    <mergeCell ref="A172:A174"/>
+    <mergeCell ref="C181:C182"/>
+    <mergeCell ref="D181:D182"/>
+    <mergeCell ref="A178:A180"/>
+    <mergeCell ref="B178:B180"/>
+    <mergeCell ref="C178:C180"/>
+    <mergeCell ref="D178:D180"/>
+    <mergeCell ref="E178:E180"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="E181:E182"/>
+    <mergeCell ref="C132:C135"/>
+    <mergeCell ref="D132:D135"/>
+    <mergeCell ref="A128:A131"/>
+    <mergeCell ref="B128:B131"/>
+    <mergeCell ref="C128:C131"/>
+    <mergeCell ref="D128:D131"/>
+    <mergeCell ref="E128:E131"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="E132:E135"/>
+    <mergeCell ref="D140:D144"/>
+    <mergeCell ref="E140:E144"/>
+    <mergeCell ref="D145:D149"/>
+    <mergeCell ref="E145:E149"/>
+    <mergeCell ref="D150:D154"/>
+    <mergeCell ref="E150:E154"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="A136:A139"/>
+    <mergeCell ref="B136:B139"/>
+    <mergeCell ref="C136:C139"/>
+    <mergeCell ref="D136:D139"/>
+    <mergeCell ref="E136:E139"/>
+    <mergeCell ref="A140:A144"/>
+    <mergeCell ref="B140:B144"/>
+    <mergeCell ref="C140:C144"/>
+    <mergeCell ref="A145:A149"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="C145:C149"/>
+    <mergeCell ref="B150:B154"/>
+    <mergeCell ref="C150:C154"/>
+    <mergeCell ref="D160:D162"/>
+    <mergeCell ref="E160:E162"/>
+    <mergeCell ref="A163:G163"/>
+    <mergeCell ref="B172:B174"/>
+    <mergeCell ref="C172:C174"/>
+    <mergeCell ref="A175:A177"/>
+    <mergeCell ref="B175:B177"/>
+    <mergeCell ref="C175:C177"/>
+    <mergeCell ref="D175:D177"/>
+    <mergeCell ref="E175:E177"/>
     <mergeCell ref="A2:G3"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="B7:B11"/>
@@ -14068,18 +13702,7 @@
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
     <mergeCell ref="E54:E55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="E60:E62"/>
     <mergeCell ref="D40:D42"/>
     <mergeCell ref="E40:E42"/>
     <mergeCell ref="D43:D44"/>
@@ -14116,81 +13739,61 @@
     <mergeCell ref="E50:E51"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="E52:E53"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="D66:D68"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="E66:E68"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
-    <mergeCell ref="E63:E65"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="D110:D112"/>
-    <mergeCell ref="E110:E112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="A116:A119"/>
-    <mergeCell ref="B116:B119"/>
-    <mergeCell ref="C116:C119"/>
-    <mergeCell ref="D116:D119"/>
-    <mergeCell ref="E116:E119"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="A126:G126"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="B120:B123"/>
-    <mergeCell ref="C120:C123"/>
-    <mergeCell ref="D120:D123"/>
-    <mergeCell ref="E120:E123"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A91:A93"/>
+    <mergeCell ref="A94:A96"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="D94:D96"/>
+    <mergeCell ref="E94:E96"/>
+    <mergeCell ref="A97:A99"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="E100:E103"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="A110:G110"/>
+    <mergeCell ref="A111:G111"/>
+    <mergeCell ref="A104:A107"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="C104:C107"/>
+    <mergeCell ref="D104:D107"/>
+    <mergeCell ref="E104:E107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="E108:E109"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
